--- a/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
+++ b/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
@@ -2,11 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="R52d31d68b02942aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="Rd2ae5411f49441f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R5a643053e0da4a06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="R6bdc8061820f4c6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="Rc53f3c0459c84cc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="R8a2e4106c13a4684"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="R52728da1ac0b45bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R06417bf507ad4e23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="Re5e2d59e3ab24f30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="Rfe22da0dad714e36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="R818039e4d96f4286"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="Ra68f4e5a81f44ac6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R32097c503c124c68"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,12 +20,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="200" formatCode="0%"/>
     <x:numFmt numFmtId="201" formatCode="0.00"/>
     <x:numFmt numFmtId="202" formatCode="0"/>
+    <x:numFmt numFmtId="203" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="204" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="27">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -96,6 +101,85 @@
       <x:color rgb="FFB42318"/>
       <x:name val="Aptos"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF9A5A00"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF2563EB"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF008000"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:sz val="8"/>
+      <x:color rgb="FF008000"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="8"/>
+      <x:color rgb="FF5B6773"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFB42318"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="15"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Aptos Display"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF9A5A00"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF008000"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF5B6773"/>
+      <x:name val="Aptos"/>
+    </x:font>
   </x:fonts>
   <x:fills count="13">
     <x:fill>
@@ -160,7 +244,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="26">
+  <x:borders count="50">
     <x:border/>
     <x:border>
       <x:left style="medium">
@@ -326,11 +410,182 @@
         <x:color rgb="FF9A5A00"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="FF9A5A00"/>
+      </x:left>
+      <x:top style="medium">
+        <x:color rgb="FF9A5A00"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="medium">
+        <x:color rgb="FF9A5A00"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="medium">
+        <x:color rgb="FF9A5A00"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF9A5A00"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="FF9A5A00"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="medium">
+        <x:color rgb="FF9A5A00"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="FF9A5A00"/>
+      </x:left>
+      <x:bottom style="medium">
+        <x:color rgb="FF9A5A00"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="medium">
+        <x:color rgb="FF9A5A00"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="medium">
+        <x:color rgb="FF9A5A00"/>
+      </x:right>
+      <x:bottom style="medium">
+        <x:color rgb="FF9A5A00"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="FF157347"/>
+      </x:left>
+      <x:top style="medium">
+        <x:color rgb="FF157347"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="medium">
+        <x:color rgb="FF157347"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="medium">
+        <x:color rgb="FF157347"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF157347"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="FF157347"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="medium">
+        <x:color rgb="FF157347"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="FF157347"/>
+      </x:left>
+      <x:bottom style="medium">
+        <x:color rgb="FF157347"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="medium">
+        <x:color rgb="FF157347"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="medium">
+        <x:color rgb="FF157347"/>
+      </x:right>
+      <x:bottom style="medium">
+        <x:color rgb="FF157347"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF9A5A00"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FF9A5A00"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF9A5A00"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FF9A5A00"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF9A5A00"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF9A5A00"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF9A5A00"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF9A5A00"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="159">
+  <x:cellXfs count="322">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -712,11 +967,404 @@
     <x:xf numFmtId="0" fontId="12" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="18" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="18" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="10" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="10" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="10" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="25" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="8" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="18" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="25" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="8" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="4">
+  <x:dxfs count="14">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -736,6 +1384,116 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFFF1CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF157347"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDFF3E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB42318"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE7E5"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF157347"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDFF3E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB42318"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE7E5"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF157347"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDFF3E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9A5A00"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF157347"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDFF3E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB42318"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE7E5"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF157347"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDFF3E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB42318"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE7E5"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -912,7 +1670,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R95e9d068776d4508"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcb2c7fc2754940e5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1174,7 +1932,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>Independent decision support · No purchase authorised · Version 2026.07.23-1 · Verified 2026-07-23</x:v>
+        <x:v>Independent decision support · No purchase authorised · Version 2026.07.23-2 · Verified 2026-07-23</x:v>
       </x:c>
       <x:c r="B3" s="9"/>
       <x:c r="C3" s="9"/>
@@ -1663,7 +2421,7 @@
     <x:mergeCell ref="A38:C39"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb075d1b4447b4ff9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redfe09991ded49c0"/>
 </x:worksheet>
 </file>
 
@@ -3189,4 +3947,2291 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="35" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="13" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="11" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="12" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="12" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="13" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="14" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="12" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="17" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="15" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="28" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="45" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="37" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>Vendor response scorecard / Toimittajavastausten pisteytys</x:v>
+      </x:c>
+      <x:c r="B1" s="5"/>
+      <x:c r="C1" s="5"/>
+      <x:c r="D1" s="5"/>
+      <x:c r="E1" s="5"/>
+      <x:c r="F1" s="5"/>
+      <x:c r="G1" s="5"/>
+      <x:c r="H1" s="5"/>
+      <x:c r="I1" s="5"/>
+      <x:c r="J1" s="5"/>
+      <x:c r="K1" s="5"/>
+      <x:c r="L1" s="5"/>
+      <x:c r="M1" s="5"/>
+      <x:c r="N1" s="5"/>
+      <x:c r="O1" s="5"/>
+      <x:c r="P1" s="5"/>
+      <x:c r="Q1" s="5"/>
+      <x:c r="R1" s="5"/>
+      <x:c r="S1" s="5"/>
+      <x:c r="T1" s="5"/>
+      <x:c r="U1" s="5"/>
+      <x:c r="V1" s="5"/>
+      <x:c r="W1" s="5"/>
+      <x:c r="X1" s="5"/>
+    </x:row>
+    <x:row r="2" ht="27" customHeight="1">
+      <x:c r="A2" s="5"/>
+      <x:c r="B2" s="5"/>
+      <x:c r="C2" s="5"/>
+      <x:c r="D2" s="5"/>
+      <x:c r="E2" s="5"/>
+      <x:c r="F2" s="5"/>
+      <x:c r="G2" s="5"/>
+      <x:c r="H2" s="5"/>
+      <x:c r="I2" s="5"/>
+      <x:c r="J2" s="5"/>
+      <x:c r="K2" s="5"/>
+      <x:c r="L2" s="5"/>
+      <x:c r="M2" s="5"/>
+      <x:c r="N2" s="5"/>
+      <x:c r="O2" s="5"/>
+      <x:c r="P2" s="5"/>
+      <x:c r="Q2" s="5"/>
+      <x:c r="R2" s="5"/>
+      <x:c r="S2" s="5"/>
+      <x:c r="T2" s="5"/>
+      <x:c r="U2" s="5"/>
+      <x:c r="V2" s="5"/>
+      <x:c r="W2" s="5"/>
+      <x:c r="X2" s="5"/>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="9" t="str">
+        <x:v>Evidence-gated comparison · Missing evidence is not zero · No response, score or purchase is implied</x:v>
+      </x:c>
+      <x:c r="B3" s="9"/>
+      <x:c r="C3" s="9"/>
+      <x:c r="D3" s="9"/>
+      <x:c r="E3" s="9"/>
+      <x:c r="F3" s="9"/>
+      <x:c r="G3" s="9"/>
+      <x:c r="H3" s="9"/>
+      <x:c r="I3" s="9"/>
+      <x:c r="J3" s="9"/>
+      <x:c r="K3" s="9"/>
+      <x:c r="L3" s="9"/>
+      <x:c r="M3" s="9"/>
+      <x:c r="N3" s="9"/>
+      <x:c r="O3" s="9"/>
+      <x:c r="P3" s="9"/>
+      <x:c r="Q3" s="9"/>
+      <x:c r="R3" s="9"/>
+      <x:c r="S3" s="9"/>
+      <x:c r="T3" s="9"/>
+      <x:c r="U3" s="9"/>
+      <x:c r="V3" s="9"/>
+      <x:c r="W3" s="9"/>
+      <x:c r="X3" s="9"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="177" t="str">
+        <x:v>CURRENT RELEASE: 4 VENDORS TRACKED · 0 SUBSTANTIVE RESPONSES · 0 SCORED · 0 PURCHASES AUTHORISED
+Keep every score blank until all six mandatory gates read PASS. A missing input is NOT SCORED, never a zero.
+FI: NYKYJULKAISU: 4 TOIMITTAJAA SEURANNASSA · 0 SISÄLLÖLLISTÄ VASTAUSTA · 0 PISTEYTETTY · 0 OSTOVALTUUTTA. Pidä pisteet tyhjinä, kunnes kaikki kuusi pakollista porttia ovat PASS-tilassa. Puuttuva tieto tarkoittaa EI PISTEYTETTY, ei nollaa.</x:v>
+      </x:c>
+      <x:c r="B5" s="178"/>
+      <x:c r="C5" s="178"/>
+      <x:c r="D5" s="178"/>
+      <x:c r="E5" s="178"/>
+      <x:c r="F5" s="178"/>
+      <x:c r="G5" s="178"/>
+      <x:c r="H5" s="178"/>
+      <x:c r="I5" s="178"/>
+      <x:c r="J5" s="178"/>
+      <x:c r="K5" s="178"/>
+      <x:c r="L5" s="178"/>
+      <x:c r="M5" s="178"/>
+      <x:c r="N5" s="178"/>
+      <x:c r="O5" s="178"/>
+      <x:c r="P5" s="178"/>
+      <x:c r="Q5" s="178"/>
+      <x:c r="R5" s="178"/>
+      <x:c r="S5" s="178"/>
+      <x:c r="T5" s="178"/>
+      <x:c r="U5" s="178"/>
+      <x:c r="V5" s="178"/>
+      <x:c r="W5" s="178"/>
+      <x:c r="X5" s="179"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="180"/>
+      <x:c r="B6" s="181"/>
+      <x:c r="C6" s="181"/>
+      <x:c r="D6" s="181"/>
+      <x:c r="E6" s="181"/>
+      <x:c r="F6" s="181"/>
+      <x:c r="G6" s="181"/>
+      <x:c r="H6" s="181"/>
+      <x:c r="I6" s="181"/>
+      <x:c r="J6" s="181"/>
+      <x:c r="K6" s="181"/>
+      <x:c r="L6" s="181"/>
+      <x:c r="M6" s="181"/>
+      <x:c r="N6" s="181"/>
+      <x:c r="O6" s="181"/>
+      <x:c r="P6" s="181"/>
+      <x:c r="Q6" s="181"/>
+      <x:c r="R6" s="181"/>
+      <x:c r="S6" s="181"/>
+      <x:c r="T6" s="181"/>
+      <x:c r="U6" s="181"/>
+      <x:c r="V6" s="181"/>
+      <x:c r="W6" s="181"/>
+      <x:c r="X6" s="182"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="183"/>
+      <x:c r="B7" s="184"/>
+      <x:c r="C7" s="184"/>
+      <x:c r="D7" s="184"/>
+      <x:c r="E7" s="184"/>
+      <x:c r="F7" s="184"/>
+      <x:c r="G7" s="184"/>
+      <x:c r="H7" s="184"/>
+      <x:c r="I7" s="184"/>
+      <x:c r="J7" s="184"/>
+      <x:c r="K7" s="184"/>
+      <x:c r="L7" s="184"/>
+      <x:c r="M7" s="184"/>
+      <x:c r="N7" s="184"/>
+      <x:c r="O7" s="184"/>
+      <x:c r="P7" s="184"/>
+      <x:c r="Q7" s="184"/>
+      <x:c r="R7" s="184"/>
+      <x:c r="S7" s="184"/>
+      <x:c r="T7" s="184"/>
+      <x:c r="U7" s="184"/>
+      <x:c r="V7" s="184"/>
+      <x:c r="W7" s="184"/>
+      <x:c r="X7" s="185"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="186" t="str">
+        <x:v>Legend / Selite</x:v>
+      </x:c>
+      <x:c r="B9" s="186"/>
+      <x:c r="C9" s="186"/>
+      <x:c r="D9" s="186"/>
+      <x:c r="E9" s="186"/>
+      <x:c r="F9" s="186"/>
+      <x:c r="H9" s="190" t="str">
+        <x:v>Gate states / Porttien tilat</x:v>
+      </x:c>
+      <x:c r="I9" s="190"/>
+      <x:c r="J9" s="190"/>
+      <x:c r="K9" s="190"/>
+      <x:c r="L9" s="190"/>
+      <x:c r="N9" s="190" t="str">
+        <x:v>Score rule / Pisteytyssääntö</x:v>
+      </x:c>
+      <x:c r="O9" s="190"/>
+      <x:c r="P9" s="190"/>
+      <x:c r="Q9" s="190"/>
+      <x:c r="R9" s="190"/>
+      <x:c r="S9" s="190"/>
+      <x:c r="T9" s="190"/>
+      <x:c r="U9" s="190"/>
+      <x:c r="V9" s="190"/>
+      <x:c r="W9" s="190"/>
+      <x:c r="X9" s="190"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="187" t="str">
+        <x:v>Blue font</x:v>
+      </x:c>
+      <x:c r="B10" s="80" t="str">
+        <x:v>Editable input</x:v>
+      </x:c>
+      <x:c r="C10" s="188" t="str">
+        <x:v>Black font</x:v>
+      </x:c>
+      <x:c r="D10" s="80" t="str">
+        <x:v>Formula</x:v>
+      </x:c>
+      <x:c r="E10" s="189" t="str">
+        <x:v>Green font</x:v>
+      </x:c>
+      <x:c r="F10" s="80" t="str">
+        <x:v>Cross-sheet link</x:v>
+      </x:c>
+      <x:c r="H10" s="80" t="str">
+        <x:v>OPEN = missing</x:v>
+      </x:c>
+      <x:c r="I10" s="80" t="str">
+        <x:v>PASS = evidenced</x:v>
+      </x:c>
+      <x:c r="J10" s="80" t="str">
+        <x:v>FAIL = rejected</x:v>
+      </x:c>
+      <x:c r="K10" s="80" t="str"/>
+      <x:c r="L10" s="80" t="str">
+        <x:v>Only PASS closes a gate</x:v>
+      </x:c>
+      <x:c r="N10" s="80" t="str">
+        <x:v>0–5 inputs are accepted only after every gate is PASS. Weighted score remains blank until then. FI: Pisteet 0–5 syötetään vasta, kun kaikki portit ovat PASS-tilassa; painotettu tulos pysyy siihen saakka tyhjänä.</x:v>
+      </x:c>
+      <x:c r="O10" s="80"/>
+      <x:c r="P10" s="80"/>
+      <x:c r="Q10" s="80"/>
+      <x:c r="R10" s="80"/>
+      <x:c r="S10" s="80"/>
+      <x:c r="T10" s="80"/>
+      <x:c r="U10" s="80"/>
+      <x:c r="V10" s="80"/>
+      <x:c r="W10" s="80"/>
+      <x:c r="X10" s="80"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="74" t="str">
+        <x:v>Vendor ID</x:v>
+      </x:c>
+      <x:c r="B13" s="74" t="str">
+        <x:v>Vendor</x:v>
+      </x:c>
+      <x:c r="C13" s="74" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="D13" s="74" t="str">
+        <x:v>Public outreach state</x:v>
+      </x:c>
+      <x:c r="E13" s="74" t="str">
+        <x:v>Sample</x:v>
+      </x:c>
+      <x:c r="F13" s="74" t="str">
+        <x:v>Data dictionary / method</x:v>
+      </x:c>
+      <x:c r="G13" s="74" t="str">
+        <x:v>Coverage matrix</x:v>
+      </x:c>
+      <x:c r="H13" s="74" t="str">
+        <x:v>Official-anchor reconciliation</x:v>
+      </x:c>
+      <x:c r="I13" s="74" t="str">
+        <x:v>Transaction-use rights</x:v>
+      </x:c>
+      <x:c r="J13" s="74" t="str">
+        <x:v>Total cost / no auto-renew</x:v>
+      </x:c>
+      <x:c r="K13" s="74" t="str">
+        <x:v>Annual country series</x:v>
+      </x:c>
+      <x:c r="L13" s="74" t="str">
+        <x:v>Metric / scope</x:v>
+      </x:c>
+      <x:c r="M13" s="74" t="str">
+        <x:v>Coverage</x:v>
+      </x:c>
+      <x:c r="N13" s="74" t="str">
+        <x:v>Methodology</x:v>
+      </x:c>
+      <x:c r="O13" s="74" t="str">
+        <x:v>Audit trail</x:v>
+      </x:c>
+      <x:c r="P13" s="74" t="str">
+        <x:v>Licence rights</x:v>
+      </x:c>
+      <x:c r="Q13" s="74" t="str">
+        <x:v>Commercial clarity</x:v>
+      </x:c>
+      <x:c r="R13" s="74" t="str">
+        <x:v>Gates passed</x:v>
+      </x:c>
+      <x:c r="S13" s="74" t="str">
+        <x:v>Score inputs</x:v>
+      </x:c>
+      <x:c r="T13" s="74" t="str">
+        <x:v>Readiness</x:v>
+      </x:c>
+      <x:c r="U13" s="74" t="str">
+        <x:v>Weighted score (0–5)</x:v>
+      </x:c>
+      <x:c r="V13" s="74" t="str">
+        <x:v>Reviewer note</x:v>
+      </x:c>
+      <x:c r="W13" s="74" t="str">
+        <x:v>Source link</x:v>
+      </x:c>
+      <x:c r="X13" s="74" t="str">
+        <x:v>Public boundary note</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="84" customHeight="1">
+      <x:c r="A14" s="80" t="str">
+        <x:v>ecig-global-market-database</x:v>
+      </x:c>
+      <x:c r="B14" s="80" t="str">
+        <x:v>ECigIntelligence</x:v>
+      </x:c>
+      <x:c r="C14" s="80" t="str">
+        <x:v>Global Market Database</x:v>
+      </x:c>
+      <x:c r="D14" s="80" t="str">
+        <x:v>REQUEST SENT · RESPONSE PENDING
+FI: PYYNTÖ LÄHETETTY · VASTAUS ODOTTAA</x:v>
+      </x:c>
+      <x:c r="E14" s="191" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="F14" s="191" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="G14" s="191" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="H14" s="191" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="I14" s="191" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="J14" s="191" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="K14" s="191"/>
+      <x:c r="L14" s="191"/>
+      <x:c r="M14" s="191"/>
+      <x:c r="N14" s="191"/>
+      <x:c r="O14" s="191"/>
+      <x:c r="P14" s="191"/>
+      <x:c r="Q14" s="191"/>
+      <x:c r="R14" s="193" t="str">
+        <x:f>COUNTIF(E14:J14,"PASS")&amp;"/6"</x:f>
+        <x:v>0/6</x:v>
+      </x:c>
+      <x:c r="S14" s="193" t="str">
+        <x:f>COUNT(K14:Q14)&amp;"/7"</x:f>
+        <x:v>0/7</x:v>
+      </x:c>
+      <x:c r="T14" s="193" t="str">
+        <x:f>IF(AND(COUNTIF(E14:J14,"PASS")=6,COUNT(K14:Q14)=7),"READY TO SCORE","NOT SCORED")</x:f>
+        <x:v>NOT SCORED</x:v>
+      </x:c>
+      <x:c r="U14" s="197" t="str">
+        <x:f>IF(T14="READY TO SCORE",ROUND(K14*$B$25+L14*$B$26+M14*$B$27+N14*$B$28+O14*$B$29+P14*$B$30+Q14*$B$31,2),"")</x:f>
+      </x:c>
+      <x:c r="V14" s="191" t="str"/>
+      <x:c r="W14" s="195" t="str">
+        <x:f>'Sources'!C6</x:f>
+        <x:v>https://ecigintelligence.com/product-category/premium-data-bundles/</x:v>
+      </x:c>
+      <x:c r="X14" s="80" t="str">
+        <x:v>Status only. No response content or unlicensed data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="84" customHeight="1">
+      <x:c r="A15" s="81" t="str">
+        <x:v>euromonitor-passport-nicotine</x:v>
+      </x:c>
+      <x:c r="B15" s="81" t="str">
+        <x:v>Euromonitor International</x:v>
+      </x:c>
+      <x:c r="C15" s="81" t="str">
+        <x:v>Passport Nicotine / e-vapour country series</x:v>
+      </x:c>
+      <x:c r="D15" s="81" t="str">
+        <x:v>REQUEST SENT · RESPONSE PENDING
+FI: PYYNTÖ LÄHETETTY · VASTAUS ODOTTAA</x:v>
+      </x:c>
+      <x:c r="E15" s="192" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="F15" s="192" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="G15" s="192" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="H15" s="192" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="I15" s="192" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="J15" s="192" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="K15" s="192"/>
+      <x:c r="L15" s="192"/>
+      <x:c r="M15" s="192"/>
+      <x:c r="N15" s="192"/>
+      <x:c r="O15" s="192"/>
+      <x:c r="P15" s="192"/>
+      <x:c r="Q15" s="192"/>
+      <x:c r="R15" s="194" t="str">
+        <x:f>COUNTIF(E15:J15,"PASS")&amp;"/6"</x:f>
+        <x:v>0/6</x:v>
+      </x:c>
+      <x:c r="S15" s="194" t="str">
+        <x:f>COUNT(K15:Q15)&amp;"/7"</x:f>
+        <x:v>0/7</x:v>
+      </x:c>
+      <x:c r="T15" s="194" t="str">
+        <x:f>IF(AND(COUNTIF(E15:J15,"PASS")=6,COUNT(K15:Q15)=7),"READY TO SCORE","NOT SCORED")</x:f>
+        <x:v>NOT SCORED</x:v>
+      </x:c>
+      <x:c r="U15" s="198" t="str">
+        <x:f>IF(T15="READY TO SCORE",ROUND(K15*$B$25+L15*$B$26+M15*$B$27+N15*$B$28+O15*$B$29+P15*$B$30+Q15*$B$31,2),"")</x:f>
+      </x:c>
+      <x:c r="V15" s="192" t="str"/>
+      <x:c r="W15" s="196" t="str">
+        <x:f>'Sources'!C9</x:f>
+        <x:v>https://www.euromonitor.com/smokeless-tobacco-e-vapour-products-and-heated-tobacco-in-denmark/report</x:v>
+      </x:c>
+      <x:c r="X15" s="81" t="str">
+        <x:v>Status only. No response content or unlicensed data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="84" customHeight="1">
+      <x:c r="A16" s="81" t="str">
+        <x:v>niq-rms-pilot</x:v>
+      </x:c>
+      <x:c r="B16" s="81" t="str">
+        <x:v>NielsenIQ</x:v>
+      </x:c>
+      <x:c r="C16" s="81" t="str">
+        <x:v>Retail Measurement Services pilot</x:v>
+      </x:c>
+      <x:c r="D16" s="81" t="str">
+        <x:v>NOT SUBMITTED · TERMS GATE
+FI: EI LÄHETETTY · EHTOPORTTI</x:v>
+      </x:c>
+      <x:c r="E16" s="192" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="F16" s="192" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="G16" s="192" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="H16" s="192" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="I16" s="192" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="J16" s="192" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="K16" s="192"/>
+      <x:c r="L16" s="192"/>
+      <x:c r="M16" s="192"/>
+      <x:c r="N16" s="192"/>
+      <x:c r="O16" s="192"/>
+      <x:c r="P16" s="192"/>
+      <x:c r="Q16" s="192"/>
+      <x:c r="R16" s="194" t="str">
+        <x:f>COUNTIF(E16:J16,"PASS")&amp;"/6"</x:f>
+        <x:v>0/6</x:v>
+      </x:c>
+      <x:c r="S16" s="194" t="str">
+        <x:f>COUNT(K16:Q16)&amp;"/7"</x:f>
+        <x:v>0/7</x:v>
+      </x:c>
+      <x:c r="T16" s="194" t="str">
+        <x:f>IF(AND(COUNTIF(E16:J16,"PASS")=6,COUNT(K16:Q16)=7),"READY TO SCORE","NOT SCORED")</x:f>
+        <x:v>NOT SCORED</x:v>
+      </x:c>
+      <x:c r="U16" s="198" t="str">
+        <x:f>IF(T16="READY TO SCORE",ROUND(K16*$B$25+L16*$B$26+M16*$B$27+N16*$B$28+O16*$B$29+P16*$B$30+Q16*$B$31,2),"")</x:f>
+      </x:c>
+      <x:c r="V16" s="192" t="str"/>
+      <x:c r="W16" s="196" t="str">
+        <x:f>'Sources'!C12</x:f>
+        <x:v>https://nielseniq.com/global/en/products/retail-measurement-services-rms/</x:v>
+      </x:c>
+      <x:c r="X16" s="81" t="str">
+        <x:v>Status only. No response content or unlicensed data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="84" customHeight="1">
+      <x:c r="A17" s="81" t="str">
+        <x:v>circana-us-tobacco-pilot</x:v>
+      </x:c>
+      <x:c r="B17" s="81" t="str">
+        <x:v>Circana</x:v>
+      </x:c>
+      <x:c r="C17" s="81" t="str">
+        <x:v>US Tobacco POS pilot</x:v>
+      </x:c>
+      <x:c r="D17" s="81" t="str">
+        <x:v>SUBMISSION CONFIRMED · RESPONSE PENDING
+FI: LÄHETYS VAHVISTETTU · VASTAUS ODOTTAA</x:v>
+      </x:c>
+      <x:c r="E17" s="192" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="F17" s="192" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="G17" s="192" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="H17" s="192" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="I17" s="192" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="J17" s="192" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="K17" s="192"/>
+      <x:c r="L17" s="192"/>
+      <x:c r="M17" s="192"/>
+      <x:c r="N17" s="192"/>
+      <x:c r="O17" s="192"/>
+      <x:c r="P17" s="192"/>
+      <x:c r="Q17" s="192"/>
+      <x:c r="R17" s="194" t="str">
+        <x:f>COUNTIF(E17:J17,"PASS")&amp;"/6"</x:f>
+        <x:v>0/6</x:v>
+      </x:c>
+      <x:c r="S17" s="194" t="str">
+        <x:f>COUNT(K17:Q17)&amp;"/7"</x:f>
+        <x:v>0/7</x:v>
+      </x:c>
+      <x:c r="T17" s="194" t="str">
+        <x:f>IF(AND(COUNTIF(E17:J17,"PASS")=6,COUNT(K17:Q17)=7),"READY TO SCORE","NOT SCORED")</x:f>
+        <x:v>NOT SCORED</x:v>
+      </x:c>
+      <x:c r="U17" s="198" t="str">
+        <x:f>IF(T17="READY TO SCORE",ROUND(K17*$B$25+L17*$B$26+M17*$B$27+N17*$B$28+O17*$B$29+P17*$B$30+Q17*$B$31,2),"")</x:f>
+      </x:c>
+      <x:c r="V17" s="192" t="str"/>
+      <x:c r="W17" s="196" t="str">
+        <x:f>'Sources'!C13</x:f>
+        <x:v>https://www.circana.com/industries/tobacco</x:v>
+      </x:c>
+      <x:c r="X17" s="81" t="str">
+        <x:v>Status only. No response content or unlicensed data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="69" t="str">
+        <x:v>Transparent criteria and weights / Läpinäkyvät kriteerit ja painot</x:v>
+      </x:c>
+      <x:c r="B20" s="69"/>
+      <x:c r="C20" s="69"/>
+      <x:c r="D20" s="69"/>
+      <x:c r="F20" s="69" t="str">
+        <x:v>Mandatory gates / Pakolliset portit</x:v>
+      </x:c>
+      <x:c r="G20" s="69"/>
+      <x:c r="H20" s="69"/>
+      <x:c r="I20" s="69"/>
+      <x:c r="J20" s="69"/>
+      <x:c r="K20" s="69"/>
+      <x:c r="L20" s="69"/>
+      <x:c r="M20" s="69"/>
+      <x:c r="N20" s="69"/>
+      <x:c r="O20" s="69"/>
+      <x:c r="P20" s="69"/>
+      <x:c r="Q20" s="69"/>
+      <x:c r="R20" s="69"/>
+      <x:c r="S20" s="69"/>
+      <x:c r="T20" s="69"/>
+      <x:c r="U20" s="69"/>
+      <x:c r="V20" s="69"/>
+      <x:c r="W20" s="69"/>
+      <x:c r="X20" s="69"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="212" t="str">
+        <x:v>Scores measure evidence utility, not vendor integrity. The public file contains no correspondence, sender identity, exact timestamps, messaging metadata, private storage references or unlicensed vendor data.
+FI: Pisteytys mittaa evidenssihyötyä, ei toimittajan luotettavuutta. Julkinen tiedosto ei sisällä viestinvaihtoa, lähettäjätietoja, tarkkoja aikaleimoja, viestitunnisteita, yksityisiä polkuja eikä lisensoimatonta toimittajadataa.</x:v>
+      </x:c>
+      <x:c r="B21" s="213"/>
+      <x:c r="C21" s="213"/>
+      <x:c r="D21" s="213"/>
+      <x:c r="E21" s="213"/>
+      <x:c r="F21" s="213"/>
+      <x:c r="G21" s="213"/>
+      <x:c r="H21" s="213"/>
+      <x:c r="I21" s="213"/>
+      <x:c r="J21" s="213"/>
+      <x:c r="K21" s="213"/>
+      <x:c r="L21" s="213"/>
+      <x:c r="M21" s="213"/>
+      <x:c r="N21" s="213"/>
+      <x:c r="O21" s="213"/>
+      <x:c r="P21" s="213"/>
+      <x:c r="Q21" s="213"/>
+      <x:c r="R21" s="213"/>
+      <x:c r="S21" s="213"/>
+      <x:c r="T21" s="213"/>
+      <x:c r="U21" s="213"/>
+      <x:c r="V21" s="213"/>
+      <x:c r="W21" s="213"/>
+      <x:c r="X21" s="214"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="215"/>
+      <x:c r="B22" s="216"/>
+      <x:c r="C22" s="216"/>
+      <x:c r="D22" s="216"/>
+      <x:c r="E22" s="216"/>
+      <x:c r="F22" s="216"/>
+      <x:c r="G22" s="216"/>
+      <x:c r="H22" s="216"/>
+      <x:c r="I22" s="216"/>
+      <x:c r="J22" s="216"/>
+      <x:c r="K22" s="216"/>
+      <x:c r="L22" s="216"/>
+      <x:c r="M22" s="216"/>
+      <x:c r="N22" s="216"/>
+      <x:c r="O22" s="216"/>
+      <x:c r="P22" s="216"/>
+      <x:c r="Q22" s="216"/>
+      <x:c r="R22" s="216"/>
+      <x:c r="S22" s="216"/>
+      <x:c r="T22" s="216"/>
+      <x:c r="U22" s="216"/>
+      <x:c r="V22" s="216"/>
+      <x:c r="W22" s="216"/>
+      <x:c r="X22" s="217"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="74" t="str">
+        <x:v>Criterion / Kriteeri</x:v>
+      </x:c>
+      <x:c r="B24" s="74" t="str">
+        <x:v>Weight / Paino</x:v>
+      </x:c>
+      <x:c r="C24" s="74" t="str">
+        <x:v>Required evidence / Vaadittu näyttö</x:v>
+      </x:c>
+      <x:c r="D24" s="74" t="str">
+        <x:v>Score anchor / Pisteankkuri</x:v>
+      </x:c>
+      <x:c r="F24" s="74" t="str">
+        <x:v>Gate ID</x:v>
+      </x:c>
+      <x:c r="G24" s="74" t="str">
+        <x:v>Gate / Portti</x:v>
+      </x:c>
+      <x:c r="H24" s="74" t="str"/>
+      <x:c r="I24" s="74" t="str"/>
+      <x:c r="J24" s="74" t="str"/>
+      <x:c r="K24" s="74" t="str"/>
+      <x:c r="L24" s="74" t="str">
+        <x:v>Acceptance threshold / Hyväksymisraja</x:v>
+      </x:c>
+      <x:c r="M24" s="74" t="str"/>
+      <x:c r="N24" s="74" t="str"/>
+      <x:c r="O24" s="74" t="str"/>
+      <x:c r="P24" s="74" t="str"/>
+      <x:c r="Q24" s="74" t="str"/>
+      <x:c r="R24" s="74" t="str"/>
+      <x:c r="S24" s="74" t="str"/>
+      <x:c r="T24" s="74" t="str"/>
+      <x:c r="U24" s="74" t="str"/>
+      <x:c r="V24" s="74" t="str"/>
+      <x:c r="W24" s="74" t="str"/>
+      <x:c r="X24" s="74" t="str"/>
+    </x:row>
+    <x:row r="25" ht="54" customHeight="1">
+      <x:c r="A25" s="80" t="str">
+        <x:v>Annual country-series fit
+FI: Sopivuus vuosittaiseen maasarjaan</x:v>
+      </x:c>
+      <x:c r="B25" s="82" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="C25" s="80" t="str">
+        <x:v>Country × year observations can support an annual sales series.</x:v>
+      </x:c>
+      <x:c r="D25" s="80" t="str">
+        <x:v>0 = unsuitable · 3 = usable with limits · 5 = decision-grade</x:v>
+      </x:c>
+      <x:c r="F25" s="80" t="str">
+        <x:v>sample</x:v>
+      </x:c>
+      <x:c r="G25" s="80" t="str">
+        <x:v>Review sample
+FI: Tarkistusnäyte</x:v>
+      </x:c>
+      <x:c r="H25" s="80"/>
+      <x:c r="I25" s="80"/>
+      <x:c r="J25" s="80"/>
+      <x:c r="K25" s="80"/>
+      <x:c r="L25" s="80" t="str">
+        <x:v>Representative rows with values, units and definitions.</x:v>
+      </x:c>
+      <x:c r="M25" s="80"/>
+      <x:c r="N25" s="80"/>
+      <x:c r="O25" s="80"/>
+      <x:c r="P25" s="80"/>
+      <x:c r="Q25" s="80"/>
+      <x:c r="R25" s="80"/>
+      <x:c r="S25" s="80"/>
+      <x:c r="T25" s="80"/>
+      <x:c r="U25" s="80"/>
+      <x:c r="V25" s="80"/>
+      <x:c r="W25" s="80"/>
+      <x:c r="X25" s="80"/>
+    </x:row>
+    <x:row r="26" ht="54" customHeight="1">
+      <x:c r="A26" s="81" t="str">
+        <x:v>Metric and scope clarity
+FI: Mittarin ja rajauksen selkeys</x:v>
+      </x:c>
+      <x:c r="B26" s="83" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="C26" s="81" t="str">
+        <x:v>Value, volume, tax basis, channels and product definitions are explicit.</x:v>
+      </x:c>
+      <x:c r="D26" s="81" t="str">
+        <x:v>0 = unsuitable · 3 = usable with limits · 5 = decision-grade</x:v>
+      </x:c>
+      <x:c r="F26" s="80" t="str">
+        <x:v>method</x:v>
+      </x:c>
+      <x:c r="G26" s="80" t="str">
+        <x:v>Data dictionary and method
+FI: Datamäärittely ja menetelmä</x:v>
+      </x:c>
+      <x:c r="H26" s="80"/>
+      <x:c r="I26" s="80"/>
+      <x:c r="J26" s="80"/>
+      <x:c r="K26" s="80"/>
+      <x:c r="L26" s="80" t="str">
+        <x:v>Definitions, methods, modelling and quality controls documented.</x:v>
+      </x:c>
+      <x:c r="M26" s="80"/>
+      <x:c r="N26" s="80"/>
+      <x:c r="O26" s="80"/>
+      <x:c r="P26" s="80"/>
+      <x:c r="Q26" s="80"/>
+      <x:c r="R26" s="80"/>
+      <x:c r="S26" s="80"/>
+      <x:c r="T26" s="80"/>
+      <x:c r="U26" s="80"/>
+      <x:c r="V26" s="80"/>
+      <x:c r="W26" s="80"/>
+      <x:c r="X26" s="80"/>
+    </x:row>
+    <x:row r="27" ht="54" customHeight="1">
+      <x:c r="A27" s="81" t="str">
+        <x:v>Country, year and product coverage
+FI: Maa-, vuosi- ja tuotekattavuus</x:v>
+      </x:c>
+      <x:c r="B27" s="83" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="C27" s="81" t="str">
+        <x:v>Coverage matrix identifies countries, years, devices and e-liquids.</x:v>
+      </x:c>
+      <x:c r="D27" s="81" t="str">
+        <x:v>0 = unsuitable · 3 = usable with limits · 5 = decision-grade</x:v>
+      </x:c>
+      <x:c r="F27" s="80" t="str">
+        <x:v>coverage</x:v>
+      </x:c>
+      <x:c r="G27" s="80" t="str">
+        <x:v>Coverage matrix
+FI: Kattavuusmatriisi</x:v>
+      </x:c>
+      <x:c r="H27" s="80"/>
+      <x:c r="I27" s="80"/>
+      <x:c r="J27" s="80"/>
+      <x:c r="K27" s="80"/>
+      <x:c r="L27" s="80" t="str">
+        <x:v>Countries, years, products and measures listed.</x:v>
+      </x:c>
+      <x:c r="M27" s="80"/>
+      <x:c r="N27" s="80"/>
+      <x:c r="O27" s="80"/>
+      <x:c r="P27" s="80"/>
+      <x:c r="Q27" s="80"/>
+      <x:c r="R27" s="80"/>
+      <x:c r="S27" s="80"/>
+      <x:c r="T27" s="80"/>
+      <x:c r="U27" s="80"/>
+      <x:c r="V27" s="80"/>
+      <x:c r="W27" s="80"/>
+      <x:c r="X27" s="80"/>
+    </x:row>
+    <x:row r="28" ht="54" customHeight="1">
+      <x:c r="A28" s="81" t="str">
+        <x:v>Methodology transparency
+FI: Menetelmän läpinäkyvyys</x:v>
+      </x:c>
+      <x:c r="B28" s="83" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="C28" s="81" t="str">
+        <x:v>Primary inputs, modelling, imputation and quality controls are reviewable.</x:v>
+      </x:c>
+      <x:c r="D28" s="81" t="str">
+        <x:v>0 = unsuitable · 3 = usable with limits · 5 = decision-grade</x:v>
+      </x:c>
+      <x:c r="F28" s="80" t="str">
+        <x:v>anchor</x:v>
+      </x:c>
+      <x:c r="G28" s="80" t="str">
+        <x:v>Official-anchor reconciliation
+FI: Täsmäytys viralliseen vertailupisteeseen</x:v>
+      </x:c>
+      <x:c r="H28" s="80"/>
+      <x:c r="I28" s="80"/>
+      <x:c r="J28" s="80"/>
+      <x:c r="K28" s="80"/>
+      <x:c r="L28" s="80" t="str">
+        <x:v>One country-year reconciles to a reviewable official anchor.</x:v>
+      </x:c>
+      <x:c r="M28" s="80"/>
+      <x:c r="N28" s="80"/>
+      <x:c r="O28" s="80"/>
+      <x:c r="P28" s="80"/>
+      <x:c r="Q28" s="80"/>
+      <x:c r="R28" s="80"/>
+      <x:c r="S28" s="80"/>
+      <x:c r="T28" s="80"/>
+      <x:c r="U28" s="80"/>
+      <x:c r="V28" s="80"/>
+      <x:c r="W28" s="80"/>
+      <x:c r="X28" s="80"/>
+    </x:row>
+    <x:row r="29" ht="54" customHeight="1">
+      <x:c r="A29" s="81" t="str">
+        <x:v>Reproducibility, export and audit trail
+FI: Toistettavuus, vienti ja auditointijälki</x:v>
+      </x:c>
+      <x:c r="B29" s="83" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="C29" s="81" t="str">
+        <x:v>Export preserves units, provenance and enough detail for reconciliation.</x:v>
+      </x:c>
+      <x:c r="D29" s="81" t="str">
+        <x:v>0 = unsuitable · 3 = usable with limits · 5 = decision-grade</x:v>
+      </x:c>
+      <x:c r="F29" s="80" t="str">
+        <x:v>rights</x:v>
+      </x:c>
+      <x:c r="G29" s="80" t="str">
+        <x:v>Transaction-use rights
+FI: Transaktiokäyttöoikeudet</x:v>
+      </x:c>
+      <x:c r="H29" s="80"/>
+      <x:c r="I29" s="80"/>
+      <x:c r="J29" s="80"/>
+      <x:c r="K29" s="80"/>
+      <x:c r="L29" s="80" t="str">
+        <x:v>Written lender, M&amp;A and data-room use rights.</x:v>
+      </x:c>
+      <x:c r="M29" s="80"/>
+      <x:c r="N29" s="80"/>
+      <x:c r="O29" s="80"/>
+      <x:c r="P29" s="80"/>
+      <x:c r="Q29" s="80"/>
+      <x:c r="R29" s="80"/>
+      <x:c r="S29" s="80"/>
+      <x:c r="T29" s="80"/>
+      <x:c r="U29" s="80"/>
+      <x:c r="V29" s="80"/>
+      <x:c r="W29" s="80"/>
+      <x:c r="X29" s="80"/>
+    </x:row>
+    <x:row r="30" ht="54" customHeight="1">
+      <x:c r="A30" s="81" t="str">
+        <x:v>Lender, M&amp;A and data-room licence rights
+FI: Rahoittaja-, M&amp;A- ja dataroom-lisenssioikeudet</x:v>
+      </x:c>
+      <x:c r="B30" s="83" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="C30" s="81" t="str">
+        <x:v>Written rights cover the intended financing and transaction review.</x:v>
+      </x:c>
+      <x:c r="D30" s="81" t="str">
+        <x:v>0 = unsuitable · 3 = usable with limits · 5 = decision-grade</x:v>
+      </x:c>
+      <x:c r="F30" s="80" t="str">
+        <x:v>commercial</x:v>
+      </x:c>
+      <x:c r="G30" s="80" t="str">
+        <x:v>Total cost and no auto-renew
+FI: Kokonaiskustannus ja ei automaattista uusintaa</x:v>
+      </x:c>
+      <x:c r="H30" s="80"/>
+      <x:c r="I30" s="80"/>
+      <x:c r="J30" s="80"/>
+      <x:c r="K30" s="80"/>
+      <x:c r="L30" s="80" t="str">
+        <x:v>Total cost, term and renewal mechanics documented.</x:v>
+      </x:c>
+      <x:c r="M30" s="80"/>
+      <x:c r="N30" s="80"/>
+      <x:c r="O30" s="80"/>
+      <x:c r="P30" s="80"/>
+      <x:c r="Q30" s="80"/>
+      <x:c r="R30" s="80"/>
+      <x:c r="S30" s="80"/>
+      <x:c r="T30" s="80"/>
+      <x:c r="U30" s="80"/>
+      <x:c r="V30" s="80"/>
+      <x:c r="W30" s="80"/>
+      <x:c r="X30" s="80"/>
+    </x:row>
+    <x:row r="31" ht="54" customHeight="1">
+      <x:c r="A31" s="81" t="str">
+        <x:v>Price, update and renewal clarity
+FI: Hinnan, päivitysten ja uusinnan selkeys</x:v>
+      </x:c>
+      <x:c r="B31" s="83" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="C31" s="81" t="str">
+        <x:v>Total cost, users, exports, updates, term and renewal are explicit.</x:v>
+      </x:c>
+      <x:c r="D31" s="81" t="str">
+        <x:v>0 = unsuitable · 3 = usable with limits · 5 = decision-grade</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:X2"/>
+    <x:mergeCell ref="A3:X3"/>
+    <x:mergeCell ref="A5:X7"/>
+    <x:mergeCell ref="A9:F9"/>
+    <x:mergeCell ref="H9:L9"/>
+    <x:mergeCell ref="N9:X9"/>
+    <x:mergeCell ref="N10:X10"/>
+    <x:mergeCell ref="A20:D20"/>
+    <x:mergeCell ref="F20:X20"/>
+    <x:mergeCell ref="G24:K24"/>
+    <x:mergeCell ref="L24:X24"/>
+    <x:mergeCell ref="G25:K25"/>
+    <x:mergeCell ref="L25:X25"/>
+    <x:mergeCell ref="G26:K26"/>
+    <x:mergeCell ref="L26:X26"/>
+    <x:mergeCell ref="G27:K27"/>
+    <x:mergeCell ref="L27:X27"/>
+    <x:mergeCell ref="G28:K28"/>
+    <x:mergeCell ref="L28:X28"/>
+    <x:mergeCell ref="G29:K29"/>
+    <x:mergeCell ref="L29:X29"/>
+    <x:mergeCell ref="G30:K30"/>
+    <x:mergeCell ref="L30:X30"/>
+    <x:mergeCell ref="A21:X22"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="E14:J17">
+    <x:cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="PASS"/>
+    <x:cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="FAIL"/>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="T14:T17">
+    <x:cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="READY"/>
+    <x:cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="NOT SCORED"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" sqref="E14:J17">
+      <x:formula1>"OPEN,PASS,FAIL"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="K14:Q17">
+      <x:formula1>0</x:formula1>
+      <x:formula2>5</x:formula2>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="25" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="15" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="42" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="28" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="35" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="17" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="20" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="18" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="17" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="42" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="37" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>Evidence intake template / Evidenssin vastaanottopohja</x:v>
+      </x:c>
+      <x:c r="B1" s="5"/>
+      <x:c r="C1" s="5"/>
+      <x:c r="D1" s="5"/>
+      <x:c r="E1" s="5"/>
+      <x:c r="F1" s="5"/>
+      <x:c r="G1" s="5"/>
+      <x:c r="H1" s="5"/>
+      <x:c r="I1" s="5"/>
+      <x:c r="J1" s="5"/>
+      <x:c r="K1" s="5"/>
+      <x:c r="L1" s="5"/>
+      <x:c r="M1" s="5"/>
+      <x:c r="N1" s="5"/>
+      <x:c r="O1" s="5"/>
+      <x:c r="P1" s="5"/>
+      <x:c r="Q1" s="5"/>
+      <x:c r="R1" s="5"/>
+      <x:c r="S1" s="5"/>
+      <x:c r="T1" s="5"/>
+      <x:c r="U1" s="5"/>
+      <x:c r="V1" s="5"/>
+      <x:c r="W1" s="5"/>
+      <x:c r="X1" s="5"/>
+    </x:row>
+    <x:row r="2" ht="27" customHeight="1">
+      <x:c r="A2" s="5"/>
+      <x:c r="B2" s="5"/>
+      <x:c r="C2" s="5"/>
+      <x:c r="D2" s="5"/>
+      <x:c r="E2" s="5"/>
+      <x:c r="F2" s="5"/>
+      <x:c r="G2" s="5"/>
+      <x:c r="H2" s="5"/>
+      <x:c r="I2" s="5"/>
+      <x:c r="J2" s="5"/>
+      <x:c r="K2" s="5"/>
+      <x:c r="L2" s="5"/>
+      <x:c r="M2" s="5"/>
+      <x:c r="N2" s="5"/>
+      <x:c r="O2" s="5"/>
+      <x:c r="P2" s="5"/>
+      <x:c r="Q2" s="5"/>
+      <x:c r="R2" s="5"/>
+      <x:c r="S2" s="5"/>
+      <x:c r="T2" s="5"/>
+      <x:c r="U2" s="5"/>
+      <x:c r="V2" s="5"/>
+      <x:c r="W2" s="5"/>
+      <x:c r="X2" s="5"/>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="9" t="str">
+        <x:v>One evidence object per row · Blank public-safe template · Complete licence and public-use review before release</x:v>
+      </x:c>
+      <x:c r="B3" s="9"/>
+      <x:c r="C3" s="9"/>
+      <x:c r="D3" s="9"/>
+      <x:c r="E3" s="9"/>
+      <x:c r="F3" s="9"/>
+      <x:c r="G3" s="9"/>
+      <x:c r="H3" s="9"/>
+      <x:c r="I3" s="9"/>
+      <x:c r="J3" s="9"/>
+      <x:c r="K3" s="9"/>
+      <x:c r="L3" s="9"/>
+      <x:c r="M3" s="9"/>
+      <x:c r="N3" s="9"/>
+      <x:c r="O3" s="9"/>
+      <x:c r="P3" s="9"/>
+      <x:c r="Q3" s="9"/>
+      <x:c r="R3" s="9"/>
+      <x:c r="S3" s="9"/>
+      <x:c r="T3" s="9"/>
+      <x:c r="U3" s="9"/>
+      <x:c r="V3" s="9"/>
+      <x:c r="W3" s="9"/>
+      <x:c r="X3" s="9"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="236" t="str">
+        <x:v>INTAKE RULE: retain the original evidence privately; enter only a controlled reference here. Do not paste correspondence, personal data, private paths or unlicensed data into a public workbook.
+FI: VASTAANOTTOSÄÄNTÖ: säilytä alkuperäinen aineisto yksityisesti ja lisää tähän vain hallittu viite. Älä liitä julkiseen työkirjaan viestinvaihtoa, henkilötietoja, yksityisiä polkuja tai lisensoimatonta dataa.</x:v>
+      </x:c>
+      <x:c r="B5" s="237"/>
+      <x:c r="C5" s="237"/>
+      <x:c r="D5" s="237"/>
+      <x:c r="E5" s="237"/>
+      <x:c r="F5" s="237"/>
+      <x:c r="G5" s="237"/>
+      <x:c r="H5" s="237"/>
+      <x:c r="I5" s="237"/>
+      <x:c r="J5" s="237"/>
+      <x:c r="K5" s="237"/>
+      <x:c r="L5" s="237"/>
+      <x:c r="M5" s="237"/>
+      <x:c r="N5" s="237"/>
+      <x:c r="O5" s="237"/>
+      <x:c r="P5" s="237"/>
+      <x:c r="Q5" s="237"/>
+      <x:c r="R5" s="237"/>
+      <x:c r="S5" s="237"/>
+      <x:c r="T5" s="237"/>
+      <x:c r="U5" s="237"/>
+      <x:c r="V5" s="237"/>
+      <x:c r="W5" s="237"/>
+      <x:c r="X5" s="238"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="239"/>
+      <x:c r="B6" s="240"/>
+      <x:c r="C6" s="240"/>
+      <x:c r="D6" s="240"/>
+      <x:c r="E6" s="240"/>
+      <x:c r="F6" s="240"/>
+      <x:c r="G6" s="240"/>
+      <x:c r="H6" s="240"/>
+      <x:c r="I6" s="240"/>
+      <x:c r="J6" s="240"/>
+      <x:c r="K6" s="240"/>
+      <x:c r="L6" s="240"/>
+      <x:c r="M6" s="240"/>
+      <x:c r="N6" s="240"/>
+      <x:c r="O6" s="240"/>
+      <x:c r="P6" s="240"/>
+      <x:c r="Q6" s="240"/>
+      <x:c r="R6" s="240"/>
+      <x:c r="S6" s="240"/>
+      <x:c r="T6" s="240"/>
+      <x:c r="U6" s="240"/>
+      <x:c r="V6" s="240"/>
+      <x:c r="W6" s="240"/>
+      <x:c r="X6" s="241"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="242"/>
+      <x:c r="B7" s="243"/>
+      <x:c r="C7" s="243"/>
+      <x:c r="D7" s="243"/>
+      <x:c r="E7" s="243"/>
+      <x:c r="F7" s="243"/>
+      <x:c r="G7" s="243"/>
+      <x:c r="H7" s="243"/>
+      <x:c r="I7" s="243"/>
+      <x:c r="J7" s="243"/>
+      <x:c r="K7" s="243"/>
+      <x:c r="L7" s="243"/>
+      <x:c r="M7" s="243"/>
+      <x:c r="N7" s="243"/>
+      <x:c r="O7" s="243"/>
+      <x:c r="P7" s="243"/>
+      <x:c r="Q7" s="243"/>
+      <x:c r="R7" s="243"/>
+      <x:c r="S7" s="243"/>
+      <x:c r="T7" s="243"/>
+      <x:c r="U7" s="243"/>
+      <x:c r="V7" s="243"/>
+      <x:c r="W7" s="243"/>
+      <x:c r="X7" s="244"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="186" t="str">
+        <x:v>Legend / Selite</x:v>
+      </x:c>
+      <x:c r="B9" s="186"/>
+      <x:c r="C9" s="186"/>
+      <x:c r="D9" s="186"/>
+      <x:c r="E9" s="186"/>
+      <x:c r="F9" s="186"/>
+      <x:c r="G9" s="186"/>
+      <x:c r="H9" s="186"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="245" t="str">
+        <x:v>Blue font</x:v>
+      </x:c>
+      <x:c r="B10" s="80" t="str">
+        <x:v>Editable input</x:v>
+      </x:c>
+      <x:c r="C10" s="188" t="str">
+        <x:v>Black font</x:v>
+      </x:c>
+      <x:c r="D10" s="80" t="str">
+        <x:v>Fixed label</x:v>
+      </x:c>
+      <x:c r="E10" s="80" t="str">
+        <x:v>One row</x:v>
+      </x:c>
+      <x:c r="F10" s="80" t="str">
+        <x:v>One evidence object</x:v>
+      </x:c>
+      <x:c r="G10" s="80" t="str">
+        <x:v>Blank</x:v>
+      </x:c>
+      <x:c r="H10" s="80" t="str">
+        <x:v>Unknown / not received</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="74" t="str">
+        <x:v>Intake ID</x:v>
+      </x:c>
+      <x:c r="B12" s="74" t="str">
+        <x:v>Intake type</x:v>
+      </x:c>
+      <x:c r="C12" s="74" t="str">
+        <x:v>Provider / Country</x:v>
+      </x:c>
+      <x:c r="D12" s="74" t="str">
+        <x:v>Received on</x:v>
+      </x:c>
+      <x:c r="E12" s="74" t="str">
+        <x:v>Evidence type</x:v>
+      </x:c>
+      <x:c r="F12" s="74" t="str">
+        <x:v>Years from</x:v>
+      </x:c>
+      <x:c r="G12" s="74" t="str">
+        <x:v>Years to</x:v>
+      </x:c>
+      <x:c r="H12" s="74" t="str">
+        <x:v>Measure</x:v>
+      </x:c>
+      <x:c r="I12" s="74" t="str">
+        <x:v>Supply-chain stage</x:v>
+      </x:c>
+      <x:c r="J12" s="74" t="str">
+        <x:v>Product scope</x:v>
+      </x:c>
+      <x:c r="K12" s="74" t="str">
+        <x:v>Geography</x:v>
+      </x:c>
+      <x:c r="L12" s="74" t="str">
+        <x:v>Currency</x:v>
+      </x:c>
+      <x:c r="M12" s="74" t="str">
+        <x:v>Unit</x:v>
+      </x:c>
+      <x:c r="N12" s="74" t="str">
+        <x:v>Raw / Derived</x:v>
+      </x:c>
+      <x:c r="O12" s="74" t="str">
+        <x:v>Controlled source or file reference</x:v>
+      </x:c>
+      <x:c r="P12" s="74" t="str">
+        <x:v>SHA-256</x:v>
+      </x:c>
+      <x:c r="Q12" s="74" t="str">
+        <x:v>Licence / Terms</x:v>
+      </x:c>
+      <x:c r="R12" s="74" t="str">
+        <x:v>Public use allowed</x:v>
+      </x:c>
+      <x:c r="S12" s="74" t="str">
+        <x:v>Reviewer</x:v>
+      </x:c>
+      <x:c r="T12" s="74" t="str">
+        <x:v>Review status</x:v>
+      </x:c>
+      <x:c r="U12" s="74" t="str">
+        <x:v>Confidence</x:v>
+      </x:c>
+      <x:c r="V12" s="74" t="str">
+        <x:v>Gaps / Notes</x:v>
+      </x:c>
+      <x:c r="W12" s="74" t="str">
+        <x:v>Public citation candidate</x:v>
+      </x:c>
+      <x:c r="X12" s="74" t="str">
+        <x:v>Public release decision</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="44" customHeight="1">
+      <x:c r="A13" s="191"/>
+      <x:c r="B13" s="191"/>
+      <x:c r="C13" s="191"/>
+      <x:c r="D13" s="246"/>
+      <x:c r="E13" s="191"/>
+      <x:c r="F13" s="248"/>
+      <x:c r="G13" s="248"/>
+      <x:c r="H13" s="191"/>
+      <x:c r="I13" s="191"/>
+      <x:c r="J13" s="191"/>
+      <x:c r="K13" s="191"/>
+      <x:c r="L13" s="191"/>
+      <x:c r="M13" s="191"/>
+      <x:c r="N13" s="191"/>
+      <x:c r="O13" s="191"/>
+      <x:c r="P13" s="191"/>
+      <x:c r="Q13" s="191"/>
+      <x:c r="R13" s="191"/>
+      <x:c r="S13" s="191"/>
+      <x:c r="T13" s="191"/>
+      <x:c r="U13" s="191"/>
+      <x:c r="V13" s="191"/>
+      <x:c r="W13" s="191"/>
+      <x:c r="X13" s="191"/>
+    </x:row>
+    <x:row r="14" ht="44" customHeight="1">
+      <x:c r="A14" s="192"/>
+      <x:c r="B14" s="192"/>
+      <x:c r="C14" s="192"/>
+      <x:c r="D14" s="247"/>
+      <x:c r="E14" s="192"/>
+      <x:c r="F14" s="249"/>
+      <x:c r="G14" s="249"/>
+      <x:c r="H14" s="192"/>
+      <x:c r="I14" s="192"/>
+      <x:c r="J14" s="192"/>
+      <x:c r="K14" s="192"/>
+      <x:c r="L14" s="192"/>
+      <x:c r="M14" s="192"/>
+      <x:c r="N14" s="192"/>
+      <x:c r="O14" s="192"/>
+      <x:c r="P14" s="192"/>
+      <x:c r="Q14" s="192"/>
+      <x:c r="R14" s="192"/>
+      <x:c r="S14" s="192"/>
+      <x:c r="T14" s="192"/>
+      <x:c r="U14" s="192"/>
+      <x:c r="V14" s="192"/>
+      <x:c r="W14" s="192"/>
+      <x:c r="X14" s="192"/>
+    </x:row>
+    <x:row r="15" ht="44" customHeight="1">
+      <x:c r="A15" s="192"/>
+      <x:c r="B15" s="192"/>
+      <x:c r="C15" s="192"/>
+      <x:c r="D15" s="247"/>
+      <x:c r="E15" s="192"/>
+      <x:c r="F15" s="249"/>
+      <x:c r="G15" s="249"/>
+      <x:c r="H15" s="192"/>
+      <x:c r="I15" s="192"/>
+      <x:c r="J15" s="192"/>
+      <x:c r="K15" s="192"/>
+      <x:c r="L15" s="192"/>
+      <x:c r="M15" s="192"/>
+      <x:c r="N15" s="192"/>
+      <x:c r="O15" s="192"/>
+      <x:c r="P15" s="192"/>
+      <x:c r="Q15" s="192"/>
+      <x:c r="R15" s="192"/>
+      <x:c r="S15" s="192"/>
+      <x:c r="T15" s="192"/>
+      <x:c r="U15" s="192"/>
+      <x:c r="V15" s="192"/>
+      <x:c r="W15" s="192"/>
+      <x:c r="X15" s="192"/>
+    </x:row>
+    <x:row r="16" ht="44" customHeight="1">
+      <x:c r="A16" s="192"/>
+      <x:c r="B16" s="192"/>
+      <x:c r="C16" s="192"/>
+      <x:c r="D16" s="247"/>
+      <x:c r="E16" s="192"/>
+      <x:c r="F16" s="249"/>
+      <x:c r="G16" s="249"/>
+      <x:c r="H16" s="192"/>
+      <x:c r="I16" s="192"/>
+      <x:c r="J16" s="192"/>
+      <x:c r="K16" s="192"/>
+      <x:c r="L16" s="192"/>
+      <x:c r="M16" s="192"/>
+      <x:c r="N16" s="192"/>
+      <x:c r="O16" s="192"/>
+      <x:c r="P16" s="192"/>
+      <x:c r="Q16" s="192"/>
+      <x:c r="R16" s="192"/>
+      <x:c r="S16" s="192"/>
+      <x:c r="T16" s="192"/>
+      <x:c r="U16" s="192"/>
+      <x:c r="V16" s="192"/>
+      <x:c r="W16" s="192"/>
+      <x:c r="X16" s="192"/>
+    </x:row>
+    <x:row r="17" ht="44" customHeight="1">
+      <x:c r="A17" s="192"/>
+      <x:c r="B17" s="192"/>
+      <x:c r="C17" s="192"/>
+      <x:c r="D17" s="247"/>
+      <x:c r="E17" s="192"/>
+      <x:c r="F17" s="249"/>
+      <x:c r="G17" s="249"/>
+      <x:c r="H17" s="192"/>
+      <x:c r="I17" s="192"/>
+      <x:c r="J17" s="192"/>
+      <x:c r="K17" s="192"/>
+      <x:c r="L17" s="192"/>
+      <x:c r="M17" s="192"/>
+      <x:c r="N17" s="192"/>
+      <x:c r="O17" s="192"/>
+      <x:c r="P17" s="192"/>
+      <x:c r="Q17" s="192"/>
+      <x:c r="R17" s="192"/>
+      <x:c r="S17" s="192"/>
+      <x:c r="T17" s="192"/>
+      <x:c r="U17" s="192"/>
+      <x:c r="V17" s="192"/>
+      <x:c r="W17" s="192"/>
+      <x:c r="X17" s="192"/>
+    </x:row>
+    <x:row r="18" ht="44" customHeight="1">
+      <x:c r="A18" s="192"/>
+      <x:c r="B18" s="192"/>
+      <x:c r="C18" s="192"/>
+      <x:c r="D18" s="247"/>
+      <x:c r="E18" s="192"/>
+      <x:c r="F18" s="249"/>
+      <x:c r="G18" s="249"/>
+      <x:c r="H18" s="192"/>
+      <x:c r="I18" s="192"/>
+      <x:c r="J18" s="192"/>
+      <x:c r="K18" s="192"/>
+      <x:c r="L18" s="192"/>
+      <x:c r="M18" s="192"/>
+      <x:c r="N18" s="192"/>
+      <x:c r="O18" s="192"/>
+      <x:c r="P18" s="192"/>
+      <x:c r="Q18" s="192"/>
+      <x:c r="R18" s="192"/>
+      <x:c r="S18" s="192"/>
+      <x:c r="T18" s="192"/>
+      <x:c r="U18" s="192"/>
+      <x:c r="V18" s="192"/>
+      <x:c r="W18" s="192"/>
+      <x:c r="X18" s="192"/>
+    </x:row>
+    <x:row r="19" ht="44" customHeight="1">
+      <x:c r="A19" s="192"/>
+      <x:c r="B19" s="192"/>
+      <x:c r="C19" s="192"/>
+      <x:c r="D19" s="247"/>
+      <x:c r="E19" s="192"/>
+      <x:c r="F19" s="249"/>
+      <x:c r="G19" s="249"/>
+      <x:c r="H19" s="192"/>
+      <x:c r="I19" s="192"/>
+      <x:c r="J19" s="192"/>
+      <x:c r="K19" s="192"/>
+      <x:c r="L19" s="192"/>
+      <x:c r="M19" s="192"/>
+      <x:c r="N19" s="192"/>
+      <x:c r="O19" s="192"/>
+      <x:c r="P19" s="192"/>
+      <x:c r="Q19" s="192"/>
+      <x:c r="R19" s="192"/>
+      <x:c r="S19" s="192"/>
+      <x:c r="T19" s="192"/>
+      <x:c r="U19" s="192"/>
+      <x:c r="V19" s="192"/>
+      <x:c r="W19" s="192"/>
+      <x:c r="X19" s="192"/>
+    </x:row>
+    <x:row r="20" ht="44" customHeight="1">
+      <x:c r="A20" s="192"/>
+      <x:c r="B20" s="192"/>
+      <x:c r="C20" s="192"/>
+      <x:c r="D20" s="247"/>
+      <x:c r="E20" s="192"/>
+      <x:c r="F20" s="249"/>
+      <x:c r="G20" s="249"/>
+      <x:c r="H20" s="192"/>
+      <x:c r="I20" s="192"/>
+      <x:c r="J20" s="192"/>
+      <x:c r="K20" s="192"/>
+      <x:c r="L20" s="192"/>
+      <x:c r="M20" s="192"/>
+      <x:c r="N20" s="192"/>
+      <x:c r="O20" s="192"/>
+      <x:c r="P20" s="192"/>
+      <x:c r="Q20" s="192"/>
+      <x:c r="R20" s="192"/>
+      <x:c r="S20" s="192"/>
+      <x:c r="T20" s="192"/>
+      <x:c r="U20" s="192"/>
+      <x:c r="V20" s="192"/>
+      <x:c r="W20" s="192"/>
+      <x:c r="X20" s="192"/>
+    </x:row>
+    <x:row r="21" ht="44" customHeight="1">
+      <x:c r="A21" s="192"/>
+      <x:c r="B21" s="192"/>
+      <x:c r="C21" s="192"/>
+      <x:c r="D21" s="247"/>
+      <x:c r="E21" s="192"/>
+      <x:c r="F21" s="249"/>
+      <x:c r="G21" s="249"/>
+      <x:c r="H21" s="192"/>
+      <x:c r="I21" s="192"/>
+      <x:c r="J21" s="192"/>
+      <x:c r="K21" s="192"/>
+      <x:c r="L21" s="192"/>
+      <x:c r="M21" s="192"/>
+      <x:c r="N21" s="192"/>
+      <x:c r="O21" s="192"/>
+      <x:c r="P21" s="192"/>
+      <x:c r="Q21" s="192"/>
+      <x:c r="R21" s="192"/>
+      <x:c r="S21" s="192"/>
+      <x:c r="T21" s="192"/>
+      <x:c r="U21" s="192"/>
+      <x:c r="V21" s="192"/>
+      <x:c r="W21" s="192"/>
+      <x:c r="X21" s="192"/>
+    </x:row>
+    <x:row r="22" ht="44" customHeight="1">
+      <x:c r="A22" s="192"/>
+      <x:c r="B22" s="192"/>
+      <x:c r="C22" s="192"/>
+      <x:c r="D22" s="247"/>
+      <x:c r="E22" s="192"/>
+      <x:c r="F22" s="249"/>
+      <x:c r="G22" s="249"/>
+      <x:c r="H22" s="192"/>
+      <x:c r="I22" s="192"/>
+      <x:c r="J22" s="192"/>
+      <x:c r="K22" s="192"/>
+      <x:c r="L22" s="192"/>
+      <x:c r="M22" s="192"/>
+      <x:c r="N22" s="192"/>
+      <x:c r="O22" s="192"/>
+      <x:c r="P22" s="192"/>
+      <x:c r="Q22" s="192"/>
+      <x:c r="R22" s="192"/>
+      <x:c r="S22" s="192"/>
+      <x:c r="T22" s="192"/>
+      <x:c r="U22" s="192"/>
+      <x:c r="V22" s="192"/>
+      <x:c r="W22" s="192"/>
+      <x:c r="X22" s="192"/>
+    </x:row>
+    <x:row r="23" ht="44" customHeight="1">
+      <x:c r="A23" s="192"/>
+      <x:c r="B23" s="192"/>
+      <x:c r="C23" s="192"/>
+      <x:c r="D23" s="247"/>
+      <x:c r="E23" s="192"/>
+      <x:c r="F23" s="249"/>
+      <x:c r="G23" s="249"/>
+      <x:c r="H23" s="192"/>
+      <x:c r="I23" s="192"/>
+      <x:c r="J23" s="192"/>
+      <x:c r="K23" s="192"/>
+      <x:c r="L23" s="192"/>
+      <x:c r="M23" s="192"/>
+      <x:c r="N23" s="192"/>
+      <x:c r="O23" s="192"/>
+      <x:c r="P23" s="192"/>
+      <x:c r="Q23" s="192"/>
+      <x:c r="R23" s="192"/>
+      <x:c r="S23" s="192"/>
+      <x:c r="T23" s="192"/>
+      <x:c r="U23" s="192"/>
+      <x:c r="V23" s="192"/>
+      <x:c r="W23" s="192"/>
+      <x:c r="X23" s="192"/>
+    </x:row>
+    <x:row r="24" ht="44" customHeight="1">
+      <x:c r="A24" s="192"/>
+      <x:c r="B24" s="192"/>
+      <x:c r="C24" s="192"/>
+      <x:c r="D24" s="247"/>
+      <x:c r="E24" s="192"/>
+      <x:c r="F24" s="249"/>
+      <x:c r="G24" s="249"/>
+      <x:c r="H24" s="192"/>
+      <x:c r="I24" s="192"/>
+      <x:c r="J24" s="192"/>
+      <x:c r="K24" s="192"/>
+      <x:c r="L24" s="192"/>
+      <x:c r="M24" s="192"/>
+      <x:c r="N24" s="192"/>
+      <x:c r="O24" s="192"/>
+      <x:c r="P24" s="192"/>
+      <x:c r="Q24" s="192"/>
+      <x:c r="R24" s="192"/>
+      <x:c r="S24" s="192"/>
+      <x:c r="T24" s="192"/>
+      <x:c r="U24" s="192"/>
+      <x:c r="V24" s="192"/>
+      <x:c r="W24" s="192"/>
+      <x:c r="X24" s="192"/>
+    </x:row>
+    <x:row r="25" ht="44" customHeight="1">
+      <x:c r="A25" s="192"/>
+      <x:c r="B25" s="192"/>
+      <x:c r="C25" s="192"/>
+      <x:c r="D25" s="247"/>
+      <x:c r="E25" s="192"/>
+      <x:c r="F25" s="249"/>
+      <x:c r="G25" s="249"/>
+      <x:c r="H25" s="192"/>
+      <x:c r="I25" s="192"/>
+      <x:c r="J25" s="192"/>
+      <x:c r="K25" s="192"/>
+      <x:c r="L25" s="192"/>
+      <x:c r="M25" s="192"/>
+      <x:c r="N25" s="192"/>
+      <x:c r="O25" s="192"/>
+      <x:c r="P25" s="192"/>
+      <x:c r="Q25" s="192"/>
+      <x:c r="R25" s="192"/>
+      <x:c r="S25" s="192"/>
+      <x:c r="T25" s="192"/>
+      <x:c r="U25" s="192"/>
+      <x:c r="V25" s="192"/>
+      <x:c r="W25" s="192"/>
+      <x:c r="X25" s="192"/>
+    </x:row>
+    <x:row r="26" ht="44" customHeight="1">
+      <x:c r="A26" s="192"/>
+      <x:c r="B26" s="192"/>
+      <x:c r="C26" s="192"/>
+      <x:c r="D26" s="247"/>
+      <x:c r="E26" s="192"/>
+      <x:c r="F26" s="249"/>
+      <x:c r="G26" s="249"/>
+      <x:c r="H26" s="192"/>
+      <x:c r="I26" s="192"/>
+      <x:c r="J26" s="192"/>
+      <x:c r="K26" s="192"/>
+      <x:c r="L26" s="192"/>
+      <x:c r="M26" s="192"/>
+      <x:c r="N26" s="192"/>
+      <x:c r="O26" s="192"/>
+      <x:c r="P26" s="192"/>
+      <x:c r="Q26" s="192"/>
+      <x:c r="R26" s="192"/>
+      <x:c r="S26" s="192"/>
+      <x:c r="T26" s="192"/>
+      <x:c r="U26" s="192"/>
+      <x:c r="V26" s="192"/>
+      <x:c r="W26" s="192"/>
+      <x:c r="X26" s="192"/>
+    </x:row>
+    <x:row r="27" ht="44" customHeight="1">
+      <x:c r="A27" s="192"/>
+      <x:c r="B27" s="192"/>
+      <x:c r="C27" s="192"/>
+      <x:c r="D27" s="247"/>
+      <x:c r="E27" s="192"/>
+      <x:c r="F27" s="249"/>
+      <x:c r="G27" s="249"/>
+      <x:c r="H27" s="192"/>
+      <x:c r="I27" s="192"/>
+      <x:c r="J27" s="192"/>
+      <x:c r="K27" s="192"/>
+      <x:c r="L27" s="192"/>
+      <x:c r="M27" s="192"/>
+      <x:c r="N27" s="192"/>
+      <x:c r="O27" s="192"/>
+      <x:c r="P27" s="192"/>
+      <x:c r="Q27" s="192"/>
+      <x:c r="R27" s="192"/>
+      <x:c r="S27" s="192"/>
+      <x:c r="T27" s="192"/>
+      <x:c r="U27" s="192"/>
+      <x:c r="V27" s="192"/>
+      <x:c r="W27" s="192"/>
+      <x:c r="X27" s="192"/>
+    </x:row>
+    <x:row r="28" ht="44" customHeight="1">
+      <x:c r="A28" s="192"/>
+      <x:c r="B28" s="192"/>
+      <x:c r="C28" s="192"/>
+      <x:c r="D28" s="247"/>
+      <x:c r="E28" s="192"/>
+      <x:c r="F28" s="249"/>
+      <x:c r="G28" s="249"/>
+      <x:c r="H28" s="192"/>
+      <x:c r="I28" s="192"/>
+      <x:c r="J28" s="192"/>
+      <x:c r="K28" s="192"/>
+      <x:c r="L28" s="192"/>
+      <x:c r="M28" s="192"/>
+      <x:c r="N28" s="192"/>
+      <x:c r="O28" s="192"/>
+      <x:c r="P28" s="192"/>
+      <x:c r="Q28" s="192"/>
+      <x:c r="R28" s="192"/>
+      <x:c r="S28" s="192"/>
+      <x:c r="T28" s="192"/>
+      <x:c r="U28" s="192"/>
+      <x:c r="V28" s="192"/>
+      <x:c r="W28" s="192"/>
+      <x:c r="X28" s="192"/>
+    </x:row>
+    <x:row r="29" ht="44" customHeight="1">
+      <x:c r="A29" s="192"/>
+      <x:c r="B29" s="192"/>
+      <x:c r="C29" s="192"/>
+      <x:c r="D29" s="247"/>
+      <x:c r="E29" s="192"/>
+      <x:c r="F29" s="249"/>
+      <x:c r="G29" s="249"/>
+      <x:c r="H29" s="192"/>
+      <x:c r="I29" s="192"/>
+      <x:c r="J29" s="192"/>
+      <x:c r="K29" s="192"/>
+      <x:c r="L29" s="192"/>
+      <x:c r="M29" s="192"/>
+      <x:c r="N29" s="192"/>
+      <x:c r="O29" s="192"/>
+      <x:c r="P29" s="192"/>
+      <x:c r="Q29" s="192"/>
+      <x:c r="R29" s="192"/>
+      <x:c r="S29" s="192"/>
+      <x:c r="T29" s="192"/>
+      <x:c r="U29" s="192"/>
+      <x:c r="V29" s="192"/>
+      <x:c r="W29" s="192"/>
+      <x:c r="X29" s="192"/>
+    </x:row>
+    <x:row r="30" ht="44" customHeight="1">
+      <x:c r="A30" s="192"/>
+      <x:c r="B30" s="192"/>
+      <x:c r="C30" s="192"/>
+      <x:c r="D30" s="247"/>
+      <x:c r="E30" s="192"/>
+      <x:c r="F30" s="249"/>
+      <x:c r="G30" s="249"/>
+      <x:c r="H30" s="192"/>
+      <x:c r="I30" s="192"/>
+      <x:c r="J30" s="192"/>
+      <x:c r="K30" s="192"/>
+      <x:c r="L30" s="192"/>
+      <x:c r="M30" s="192"/>
+      <x:c r="N30" s="192"/>
+      <x:c r="O30" s="192"/>
+      <x:c r="P30" s="192"/>
+      <x:c r="Q30" s="192"/>
+      <x:c r="R30" s="192"/>
+      <x:c r="S30" s="192"/>
+      <x:c r="T30" s="192"/>
+      <x:c r="U30" s="192"/>
+      <x:c r="V30" s="192"/>
+      <x:c r="W30" s="192"/>
+      <x:c r="X30" s="192"/>
+    </x:row>
+    <x:row r="31" ht="44" customHeight="1">
+      <x:c r="A31" s="192"/>
+      <x:c r="B31" s="192"/>
+      <x:c r="C31" s="192"/>
+      <x:c r="D31" s="247"/>
+      <x:c r="E31" s="192"/>
+      <x:c r="F31" s="249"/>
+      <x:c r="G31" s="249"/>
+      <x:c r="H31" s="192"/>
+      <x:c r="I31" s="192"/>
+      <x:c r="J31" s="192"/>
+      <x:c r="K31" s="192"/>
+      <x:c r="L31" s="192"/>
+      <x:c r="M31" s="192"/>
+      <x:c r="N31" s="192"/>
+      <x:c r="O31" s="192"/>
+      <x:c r="P31" s="192"/>
+      <x:c r="Q31" s="192"/>
+      <x:c r="R31" s="192"/>
+      <x:c r="S31" s="192"/>
+      <x:c r="T31" s="192"/>
+      <x:c r="U31" s="192"/>
+      <x:c r="V31" s="192"/>
+      <x:c r="W31" s="192"/>
+      <x:c r="X31" s="192"/>
+    </x:row>
+    <x:row r="32" ht="44" customHeight="1">
+      <x:c r="A32" s="192"/>
+      <x:c r="B32" s="192"/>
+      <x:c r="C32" s="192"/>
+      <x:c r="D32" s="247"/>
+      <x:c r="E32" s="192"/>
+      <x:c r="F32" s="249"/>
+      <x:c r="G32" s="249"/>
+      <x:c r="H32" s="192"/>
+      <x:c r="I32" s="192"/>
+      <x:c r="J32" s="192"/>
+      <x:c r="K32" s="192"/>
+      <x:c r="L32" s="192"/>
+      <x:c r="M32" s="192"/>
+      <x:c r="N32" s="192"/>
+      <x:c r="O32" s="192"/>
+      <x:c r="P32" s="192"/>
+      <x:c r="Q32" s="192"/>
+      <x:c r="R32" s="192"/>
+      <x:c r="S32" s="192"/>
+      <x:c r="T32" s="192"/>
+      <x:c r="U32" s="192"/>
+      <x:c r="V32" s="192"/>
+      <x:c r="W32" s="192"/>
+      <x:c r="X32" s="192"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:X2"/>
+    <x:mergeCell ref="A3:X3"/>
+    <x:mergeCell ref="A5:X7"/>
+    <x:mergeCell ref="A9:H9"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="R13:R32">
+    <x:cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="YES"/>
+    <x:cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="NO"/>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="X13:X32">
+    <x:cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="PUBLIC-SAFE"/>
+    <x:cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="DO NOT PUBLISH"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="7">
+    <x:dataValidation type="list" sqref="B13:B32">
+      <x:formula1>"VENDOR SAMPLE,COUNTRY RESPONSE,PUBLIC AUTHORITY EXTRACT,OTHER"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E13:E32">
+      <x:formula1>"SAMPLE,METHOD,COVERAGE,QUOTE,LICENCE,OFFICIAL DATA,OTHER"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="N13:N32">
+      <x:formula1>"RAW,DERIVED,MIXED,UNKNOWN"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="R13:R32">
+      <x:formula1>"YES,NO,UNKNOWN"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="T13:T32">
+      <x:formula1>"RECEIVED,SCREENING,ACCEPTED,REJECTED,HELD"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="U13:U32">
+      <x:formula1>"HIGH,MEDIUM,LOW,NOT ASSESSED"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="X13:X32">
+      <x:formula1>"DO NOT PUBLISH,PUBLIC-SAFE,LEGAL REVIEW,HELD"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="70" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>Workbook controls and audit checks / Työkirjan kontrollit ja tarkistukset</x:v>
+      </x:c>
+      <x:c r="B1" s="5"/>
+      <x:c r="C1" s="5"/>
+      <x:c r="D1" s="5"/>
+      <x:c r="E1" s="5"/>
+      <x:c r="F1" s="5"/>
+      <x:c r="G1" s="5"/>
+    </x:row>
+    <x:row r="2" ht="27" customHeight="1">
+      <x:c r="A2" s="5"/>
+      <x:c r="B2" s="5"/>
+      <x:c r="C2" s="5"/>
+      <x:c r="D2" s="5"/>
+      <x:c r="E2" s="5"/>
+      <x:c r="F2" s="5"/>
+      <x:c r="G2" s="5"/>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="9" t="str">
+        <x:v>One assertion per row · Formula-driven controls · Builder formula-error scan reported separately below</x:v>
+      </x:c>
+      <x:c r="B3" s="9"/>
+      <x:c r="C3" s="9"/>
+      <x:c r="D3" s="9"/>
+      <x:c r="E3" s="9"/>
+      <x:c r="F3" s="9"/>
+      <x:c r="G3" s="9"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="278" t="str">
+        <x:f>IF(COUNTIF(F12:F20,"FAIL")=0,"MODEL STATUS: OK / MALLIN TILA: OK","MODEL STATUS: REVIEW / MALLIN TILA: TARKISTA")</x:f>
+        <x:v>MODEL STATUS: OK / MALLIN TILA: OK</x:v>
+      </x:c>
+      <x:c r="B5" s="279"/>
+      <x:c r="C5" s="279"/>
+      <x:c r="D5" s="279"/>
+      <x:c r="E5" s="279"/>
+      <x:c r="F5" s="279"/>
+      <x:c r="G5" s="280"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="281"/>
+      <x:c r="B6" s="282"/>
+      <x:c r="C6" s="282"/>
+      <x:c r="D6" s="282"/>
+      <x:c r="E6" s="282"/>
+      <x:c r="F6" s="282"/>
+      <x:c r="G6" s="283"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="284"/>
+      <x:c r="B7" s="285"/>
+      <x:c r="C7" s="285"/>
+      <x:c r="D7" s="285"/>
+      <x:c r="E7" s="285"/>
+      <x:c r="F7" s="285"/>
+      <x:c r="G7" s="286"/>
+    </x:row>
+    <x:row r="9" ht="44" customHeight="1">
+      <x:c r="A9" s="294" t="str">
+        <x:v>A check can pass while commercial evidence is still missing. It verifies workbook logic and control design, not a vendor or purchase decision.
+FI: Tarkistus voi läpäistä, vaikka kaupallista evidenssiä puuttuisi. Se varmistaa työkirjan logiikan ja kontrollit, ei toimittajaa tai ostopäätöstä.</x:v>
+      </x:c>
+      <x:c r="B9" s="295"/>
+      <x:c r="C9" s="295"/>
+      <x:c r="D9" s="295"/>
+      <x:c r="E9" s="295"/>
+      <x:c r="F9" s="295"/>
+      <x:c r="G9" s="296"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="74" t="str">
+        <x:v>Assertion / Tarkistus</x:v>
+      </x:c>
+      <x:c r="B11" s="74" t="str">
+        <x:v>Actual / Toteuma</x:v>
+      </x:c>
+      <x:c r="C11" s="74" t="str">
+        <x:v>Expected / Odotus</x:v>
+      </x:c>
+      <x:c r="D11" s="74" t="str">
+        <x:v>Difference / Ero</x:v>
+      </x:c>
+      <x:c r="E11" s="74" t="str">
+        <x:v>Tolerance / Toleranssi</x:v>
+      </x:c>
+      <x:c r="F11" s="74" t="str">
+        <x:v>Status / Tila</x:v>
+      </x:c>
+      <x:c r="G11" s="74" t="str">
+        <x:v>Notes / Huomio</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="48" customHeight="1">
+      <x:c r="A12" s="80" t="str">
+        <x:v>Response criteria weights total</x:v>
+      </x:c>
+      <x:c r="B12" s="299" t="n">
+        <x:f>SUM('Response Scorecard'!$B$25:$B$31)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="300" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D12" s="301" t="n">
+        <x:f>B12-C12</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E12" s="301" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F12" s="193" t="str">
+        <x:f>IF(ABS(D12)&lt;=E12,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G12" s="80" t="str">
+        <x:v>Must equal 100%.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="48" customHeight="1">
+      <x:c r="A13" s="81" t="str">
+        <x:v>Tracked vendor records</x:v>
+      </x:c>
+      <x:c r="B13" s="302" t="n">
+        <x:f>COUNTA('Response Scorecard'!$A$14:$A$17)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C13" s="97" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D13" s="198" t="n">
+        <x:f>B13-C13</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="198" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="194" t="str">
+        <x:f>IF(ABS(D13)&lt;=E13,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G13" s="81" t="str">
+        <x:v>Current public shortlist contains exactly four response records.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="48" customHeight="1">
+      <x:c r="A14" s="81" t="str">
+        <x:v>Scores shown without readiness</x:v>
+      </x:c>
+      <x:c r="B14" s="302" t="n">
+        <x:f>COUNT('Response Scorecard'!$U$14:$U$17)-COUNTIF('Response Scorecard'!$T$14:$T$17,"READY TO SCORE")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C14" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="198" t="n">
+        <x:f>B14-C14</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" s="198" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="194" t="str">
+        <x:f>IF(ABS(D14)&lt;=E14,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G14" s="81" t="str">
+        <x:v>A numeric score may appear only when readiness is READY TO SCORE.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="48" customHeight="1">
+      <x:c r="A15" s="81" t="str">
+        <x:v>Purchases authorised</x:v>
+      </x:c>
+      <x:c r="B15" s="302" t="n">
+        <x:f>COUNTIF('Response Scorecard'!$T$14:$T$17,"PURCHASE AUTHORISED")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="198" t="n">
+        <x:f>B15-C15</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="198" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="194" t="str">
+        <x:f>IF(ABS(D15)&lt;=E15,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G15" s="81" t="str">
+        <x:v>This workbook grants no purchase authority.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="48" customHeight="1">
+      <x:c r="A16" s="81" t="str">
+        <x:v>Missing vendor IDs</x:v>
+      </x:c>
+      <x:c r="B16" s="302" t="n">
+        <x:f>COUNTBLANK('Response Scorecard'!$A$14:$A$17)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C16" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="198" t="n">
+        <x:f>B16-C16</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="198" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="194" t="str">
+        <x:f>IF(ABS(D16)&lt;=E16,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G16" s="81" t="str">
+        <x:v>Every tracked vendor must have a stable public ID.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="48" customHeight="1">
+      <x:c r="A17" s="81" t="str">
+        <x:v>Invalid gate states</x:v>
+      </x:c>
+      <x:c r="B17" s="302" t="n">
+        <x:f>24-COUNTIF('Response Scorecard'!$E$14:$J$17,"OPEN")-COUNTIF('Response Scorecard'!$E$14:$J$17,"PASS")-COUNTIF('Response Scorecard'!$E$14:$J$17,"FAIL")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C17" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="198" t="n">
+        <x:f>B17-C17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="198" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="194" t="str">
+        <x:f>IF(ABS(D17)&lt;=E17,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G17" s="81" t="str">
+        <x:v>Allowed values are OPEN, PASS and FAIL.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="48" customHeight="1">
+      <x:c r="A18" s="81" t="str">
+        <x:v>Out-of-range score inputs</x:v>
+      </x:c>
+      <x:c r="B18" s="302" t="n">
+        <x:f>COUNTIF('Response Scorecard'!$K$14:$Q$17,"&lt;0")+COUNTIF('Response Scorecard'!$K$14:$Q$17,"&gt;5")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C18" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="198" t="n">
+        <x:f>B18-C18</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="198" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F18" s="194" t="str">
+        <x:f>IF(ABS(D18)&lt;=E18,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G18" s="81" t="str">
+        <x:v>Score inputs must be blank or 0–5.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="48" customHeight="1">
+      <x:c r="A19" s="81" t="str">
+        <x:v>Ready rows without weighted score</x:v>
+      </x:c>
+      <x:c r="B19" s="302" t="n">
+        <x:f>COUNTIF('Response Scorecard'!$T$14:$T$17,"READY TO SCORE")-COUNT('Response Scorecard'!$U$14:$U$17)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C19" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D19" s="198" t="n">
+        <x:f>B19-C19</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" s="198" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="194" t="str">
+        <x:f>IF(ABS(D19)&lt;=E19,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G19" s="81" t="str">
+        <x:v>Every READY TO SCORE row must calculate a score.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="48" customHeight="1">
+      <x:c r="A20" s="81" t="str">
+        <x:v>Intake rows with provider but no ID</x:v>
+      </x:c>
+      <x:c r="B20" s="302" t="n">
+        <x:f>COUNTIFS('Intake Template'!$C$13:$C$32,"&lt;&gt;",'Intake Template'!$A$13:$A$32,"")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C20" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D20" s="198" t="n">
+        <x:f>B20-C20</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E20" s="198" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F20" s="194" t="str">
+        <x:f>IF(ABS(D20)&lt;=E20,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G20" s="81" t="str">
+        <x:v>Each populated intake row requires an Intake ID.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="69" t="str">
+        <x:v>Builder verification / Rakentajan varmennus</x:v>
+      </x:c>
+      <x:c r="B22" s="69"/>
+      <x:c r="C22" s="69"/>
+      <x:c r="D22" s="69"/>
+      <x:c r="E22" s="69"/>
+      <x:c r="F22" s="69"/>
+      <x:c r="G22" s="69"/>
+    </x:row>
+    <x:row r="23" ht="36" customHeight="1">
+      <x:c r="A23" s="316" t="str">
+        <x:v>The build script inspects key ranges, scans for common Excel formula-error tokens, and renders every worksheet before export. Rerun the builder after structural edits. This note does not replace a fresh scan after manual workbook changes.
+FI: Rakennusskripti tarkistaa avainalueet, etsii kaavavirheet ja renderöi jokaisen välilehden ennen vientiä. Aja rakentaja uudelleen rakenteellisten muutosten jälkeen; huomautus ei korvaa uutta tarkistusta manuaalisten muutosten jälkeen.</x:v>
+      </x:c>
+      <x:c r="B23" s="317"/>
+      <x:c r="C23" s="317"/>
+      <x:c r="D23" s="317"/>
+      <x:c r="E23" s="317"/>
+      <x:c r="F23" s="317"/>
+      <x:c r="G23" s="318"/>
+    </x:row>
+    <x:row r="24" ht="36" customHeight="1">
+      <x:c r="A24" s="319"/>
+      <x:c r="B24" s="320"/>
+      <x:c r="C24" s="320"/>
+      <x:c r="D24" s="320"/>
+      <x:c r="E24" s="320"/>
+      <x:c r="F24" s="320"/>
+      <x:c r="G24" s="321"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:G2"/>
+    <x:mergeCell ref="A3:G3"/>
+    <x:mergeCell ref="A5:G7"/>
+    <x:mergeCell ref="A9:G9"/>
+    <x:mergeCell ref="A22:G22"/>
+    <x:mergeCell ref="A23:G24"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="F12:F20">
+    <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="OK"/>
+    <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="FAIL"/>
+  </x:conditionalFormatting>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
+++ b/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="R8a2e4106c13a4684"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="R52728da1ac0b45bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R06417bf507ad4e23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="Re5e2d59e3ab24f30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="Rfe22da0dad714e36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="R818039e4d96f4286"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="Ra68f4e5a81f44ac6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R32097c503c124c68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="R0bb919f1139f4b8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="Rb2f9ec28e3474177"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R414632c4bb804573"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="Ra24af6cb5595407d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="Rf860bcb4d2714fc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="R6df8d659e0f54b96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="Rdabef7ed34a54703"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R5cad254ac9194d80"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1670,7 +1670,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcb2c7fc2754940e5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R84a179cd20764700"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1932,7 +1932,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>Independent decision support · No purchase authorised · Version 2026.07.23-2 · Verified 2026-07-23</x:v>
+        <x:v>Independent decision support · No purchase authorised · Version 2026.07.23-3 · Verified 2026-07-23</x:v>
       </x:c>
       <x:c r="B3" s="9"/>
       <x:c r="C3" s="9"/>
@@ -2421,7 +2421,7 @@
     <x:mergeCell ref="A38:C39"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redfe09991ded49c0"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24804cbbbfa44877"/>
 </x:worksheet>
 </file>
 
@@ -4035,7 +4035,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>Evidence-gated comparison · Missing evidence is not zero · No response, score or purchase is implied</x:v>
+        <x:v>Evidence-gated comparison · Missing evidence is not zero · No substantive response, score or purchase is implied</x:v>
       </x:c>
       <x:c r="B3" s="9"/>
       <x:c r="C3" s="9"/>
@@ -4063,9 +4063,9 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="177" t="str">
-        <x:v>CURRENT RELEASE: 4 VENDORS TRACKED · 0 SUBSTANTIVE RESPONSES · 0 SCORED · 0 PURCHASES AUTHORISED
+        <x:v>CURRENT RELEASE: 4 VENDORS TRACKED · 1 ADMINISTRATIVE QUALIFICATION · 0 SUBSTANTIVE RESPONSES · 0 SCORED · 0 PURCHASES AUTHORISED
 Keep every score blank until all six mandatory gates read PASS. A missing input is NOT SCORED, never a zero.
-FI: NYKYJULKAISU: 4 TOIMITTAJAA SEURANNASSA · 0 SISÄLLÖLLISTÄ VASTAUSTA · 0 PISTEYTETTY · 0 OSTOVALTUUTTA. Pidä pisteet tyhjinä, kunnes kaikki kuusi pakollista porttia ovat PASS-tilassa. Puuttuva tieto tarkoittaa EI PISTEYTETTY, ei nollaa.</x:v>
+FI: NYKYJULKAISU: 4 TOIMITTAJAA SEURANNASSA · 1 HALLINNOLLINEN TAUSTAKYSELY · 0 SISÄLLÖLLISTÄ VASTAUSTA · 0 PISTEYTETTY · 0 OSTOVALTUUTTA. Pidä pisteet tyhjinä, kunnes kaikki kuusi pakollista porttia ovat PASS-tilassa. Puuttuva tieto tarkoittaa EI PISTEYTETTY, ei nollaa.</x:v>
       </x:c>
       <x:c r="B5" s="178"/>
       <x:c r="C5" s="178"/>
@@ -4367,8 +4367,8 @@
         <x:v>Passport Nicotine / e-vapour country series</x:v>
       </x:c>
       <x:c r="D15" s="81" t="str">
-        <x:v>REQUEST SENT · RESPONSE PENDING
-FI: PYYNTÖ LÄHETETTY · VASTAUS ODOTTAA</x:v>
+        <x:v>ADMINISTRATIVE QUALIFICATION RECEIVED · CLARIFICATION SENT · ROUTING PENDING
+FI: HALLINNOLLINEN TAUSTAKYSELY VASTAANOTETTU · TÄSMENNYS LÄHETETTY · OHJAUS ODOTTAA</x:v>
       </x:c>
       <x:c r="E15" s="192" t="str">
         <x:v>OPEN</x:v>
@@ -4416,7 +4416,7 @@
         <x:v>https://www.euromonitor.com/smokeless-tobacco-e-vapour-products-and-heated-tobacco-in-denmark/report</x:v>
       </x:c>
       <x:c r="X15" s="81" t="str">
-        <x:v>Status only. No response content or unlicensed data.</x:v>
+        <x:v>Status only. Administrative qualification received; clarification sent; no sample, quote, data, method, coverage, licence, price or commitment.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="84" customHeight="1">

--- a/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
+++ b/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="R0bb919f1139f4b8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="Rb2f9ec28e3474177"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R414632c4bb804573"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="Ra24af6cb5595407d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="Rf860bcb4d2714fc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="R6df8d659e0f54b96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="Rdabef7ed34a54703"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R5cad254ac9194d80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="R3612ab6df5334d8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="Rcb5e29e196a14b25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R3de4480119934149"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="Rfe7e2381ea294bd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R197dad0d1bd34b38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="Rf91810533f994e1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="Raff6abe98337446a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R0732207a84b240a0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1371,7 +1371,7 @@
         <x:color rgb="FF157347"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDFF3E8"/>
         </x:patternFill>
       </x:fill>
@@ -1382,7 +1382,7 @@
         <x:color rgb="FF9A5A00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF1CC"/>
         </x:patternFill>
       </x:fill>
@@ -1393,7 +1393,7 @@
         <x:color rgb="FF157347"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDFF3E8"/>
         </x:patternFill>
       </x:fill>
@@ -1404,7 +1404,7 @@
         <x:color rgb="FFB42318"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE7E5"/>
         </x:patternFill>
       </x:fill>
@@ -1415,7 +1415,7 @@
         <x:color rgb="FF157347"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDFF3E8"/>
         </x:patternFill>
       </x:fill>
@@ -1426,7 +1426,7 @@
         <x:color rgb="FFB42318"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE7E5"/>
         </x:patternFill>
       </x:fill>
@@ -1437,7 +1437,7 @@
         <x:color rgb="FF157347"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDFF3E8"/>
         </x:patternFill>
       </x:fill>
@@ -1448,7 +1448,7 @@
         <x:color rgb="FF9A5A00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF1CC"/>
         </x:patternFill>
       </x:fill>
@@ -1459,7 +1459,7 @@
         <x:color rgb="FF157347"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDFF3E8"/>
         </x:patternFill>
       </x:fill>
@@ -1470,7 +1470,7 @@
         <x:color rgb="FFB42318"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE7E5"/>
         </x:patternFill>
       </x:fill>
@@ -1481,7 +1481,7 @@
         <x:color rgb="FF157347"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDFF3E8"/>
         </x:patternFill>
       </x:fill>
@@ -1492,7 +1492,7 @@
         <x:color rgb="FFB42318"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE7E5"/>
         </x:patternFill>
       </x:fill>
@@ -1503,7 +1503,7 @@
         <x:color rgb="FF157347"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDFF3E8"/>
         </x:patternFill>
       </x:fill>
@@ -1514,7 +1514,7 @@
         <x:color rgb="FFB42318"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE7E5"/>
         </x:patternFill>
       </x:fill>
@@ -1670,7 +1670,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R84a179cd20764700"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcb4fee9542144855"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1932,7 +1932,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>Independent decision support · No purchase authorised · Version 2026.07.23-3 · Verified 2026-07-23</x:v>
+        <x:v>Independent decision support · No purchase authorised · Version 2026.07.24-19 · Verified 2026-07-24</x:v>
       </x:c>
       <x:c r="B3" s="9"/>
       <x:c r="C3" s="9"/>
@@ -2421,7 +2421,7 @@
     <x:mergeCell ref="A38:C39"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24804cbbbfa44877"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb4e138282d64d1b"/>
 </x:worksheet>
 </file>
 
@@ -4035,7 +4035,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>Evidence-gated comparison · Missing evidence is not zero · No substantive response, score or purchase is implied</x:v>
+        <x:v>Evidence-gated comparison · Missing evidence is not zero · A response is not a score or purchase</x:v>
       </x:c>
       <x:c r="B3" s="9"/>
       <x:c r="C3" s="9"/>
@@ -4063,9 +4063,9 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="177" t="str">
-        <x:v>CURRENT RELEASE: 4 VENDORS TRACKED · 1 ADMINISTRATIVE QUALIFICATION · 0 SUBSTANTIVE RESPONSES · 0 SCORED · 0 PURCHASES AUTHORISED
+        <x:v>CURRENT RELEASE: 4 VENDORS TRACKED · 1 SUBSTANTIVE RESPONSE · 0 SCORED · 0 PURCHASES AUTHORISED
 Keep every score blank until all six mandatory gates read PASS. A missing input is NOT SCORED, never a zero.
-FI: NYKYJULKAISU: 4 TOIMITTAJAA SEURANNASSA · 1 HALLINNOLLINEN TAUSTAKYSELY · 0 SISÄLLÖLLISTÄ VASTAUSTA · 0 PISTEYTETTY · 0 OSTOVALTUUTTA. Pidä pisteet tyhjinä, kunnes kaikki kuusi pakollista porttia ovat PASS-tilassa. Puuttuva tieto tarkoittaa EI PISTEYTETTY, ei nollaa.</x:v>
+FI: NYKYJULKAISU: 4 TOIMITTAJAA SEURANNASSA · 1 SISÄLLÖLLINEN VASTAUS · 0 PISTEYTETTY · 0 OSTOVALTUUTTA. Pidä pisteet tyhjinä, kunnes kaikki kuusi pakollista porttia ovat PASS-tilassa. Puuttuva tieto tarkoittaa EI PISTEYTETTY, ei nollaa.</x:v>
       </x:c>
       <x:c r="B5" s="178"/>
       <x:c r="C5" s="178"/>
@@ -4304,8 +4304,8 @@
         <x:v>Global Market Database</x:v>
       </x:c>
       <x:c r="D14" s="80" t="str">
-        <x:v>REQUEST SENT · RESPONSE PENDING
-FI: PYYNTÖ LÄHETETTY · VASTAUS ODOTTAA</x:v>
+        <x:v>REQUEST SENT · NO RESPONSE OR AUTO-ACK · FOLLOW-UP 2026-07-28
+FI: PYYNTÖ LÄHETETTY · EI VASTAUSTA TAI AUTOMAATTIKUITTAUSTA · SEURANTA 2026-07-28</x:v>
       </x:c>
       <x:c r="E14" s="191" t="str">
         <x:v>OPEN</x:v>
@@ -4353,7 +4353,7 @@
         <x:v>https://ecigintelligence.com/product-category/premium-data-bundles/</x:v>
       </x:c>
       <x:c r="X14" s="80" t="str">
-        <x:v>Status only. No response content or unlicensed data.</x:v>
+        <x:v>Status only. Request sent 2026-07-23; no bounce, automated acknowledgement, response content or unlicensed data. First follow-up due 2026-07-28 if unanswered.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="84" customHeight="1">
@@ -4367,8 +4367,8 @@
         <x:v>Passport Nicotine / e-vapour country series</x:v>
       </x:c>
       <x:c r="D15" s="81" t="str">
-        <x:v>ADMINISTRATIVE QUALIFICATION RECEIVED · CLARIFICATION SENT · ROUTING PENDING
-FI: HALLINNOLLINEN TAUSTAKYSELY VASTAANOTETTU · TÄSMENNYS LÄHETETTY · OHJAUS ODOTTAA</x:v>
+        <x:v>WRITTEN RESPONSE + BROCHURE RECEIVED · MULTI-OPTION QUOTE + NUMERICAL SAMPLE REQUEST SENT · RESPONSE PENDING
+FI: KIRJALLINEN VASTAUS + ESITE SAATU · MONIVAIHTOEHTOINEN TARJOUS + NUMEERINEN NÄYTE PYYDETTY · VASTAUS ODOTTAA</x:v>
       </x:c>
       <x:c r="E15" s="192" t="str">
         <x:v>OPEN</x:v>
@@ -4416,7 +4416,7 @@
         <x:v>https://www.euromonitor.com/smokeless-tobacco-e-vapour-products-and-heated-tobacco-in-denmark/report</x:v>
       </x:c>
       <x:c r="X15" s="81" t="str">
-        <x:v>Status only. Administrative qualification received; clarification sent; no sample, quote, data, method, coverage, licence, price or commitment.</x:v>
+        <x:v>Status only. A follow-up requesting a multi-option quote and numerical sample was sent. The 8-page brochure documents an overall 100-country Passport Tobacco list, not verified e-vapour product-country coverage, plus e-vapour taxonomy and series periods. The numerical sample, itemised price, detailed method, licence terms and verified e-vapour product-country coverage remain pending. No usable data, purchase or commitment.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="84" customHeight="1">

--- a/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
+++ b/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="R3612ab6df5334d8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="Rcb5e29e196a14b25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R3de4480119934149"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="Rfe7e2381ea294bd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R197dad0d1bd34b38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="Rf91810533f994e1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="Raff6abe98337446a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R0732207a84b240a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="R6754c2daa8c8400a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="R1d336904d8984832"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R26c4b43fcc484d44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="Rdc07a01ec4654730"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R535c176df1d84bf6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="R654d681a94484298"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="R50ffb1cc01184466"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="Rf382c8cd378e46b1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1670,7 +1670,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcb4fee9542144855"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcd1ad43f84c048f7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1932,7 +1932,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>Independent decision support · No purchase authorised · Version 2026.07.24-19 · Verified 2026-07-24</x:v>
+        <x:v>Independent decision support · No purchase authorised · Version 2026.07.24-20 · Verified 2026-07-24</x:v>
       </x:c>
       <x:c r="B3" s="9"/>
       <x:c r="C3" s="9"/>
@@ -2421,7 +2421,7 @@
     <x:mergeCell ref="A38:C39"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb4e138282d64d1b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28bb7e5b6b554ff5"/>
 </x:worksheet>
 </file>
 
@@ -4063,9 +4063,9 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="177" t="str">
-        <x:v>CURRENT RELEASE: 4 VENDORS TRACKED · 1 SUBSTANTIVE RESPONSE · 0 SCORED · 0 PURCHASES AUTHORISED
+        <x:v>CURRENT RELEASE: 4 VENDORS TRACKED · 1 VENDOR ROUTE WITH SUBSTANTIVE RESPONSES · 0 SCORED · 0 PURCHASES AUTHORISED
 Keep every score blank until all six mandatory gates read PASS. A missing input is NOT SCORED, never a zero.
-FI: NYKYJULKAISU: 4 TOIMITTAJAA SEURANNASSA · 1 SISÄLLÖLLINEN VASTAUS · 0 PISTEYTETTY · 0 OSTOVALTUUTTA. Pidä pisteet tyhjinä, kunnes kaikki kuusi pakollista porttia ovat PASS-tilassa. Puuttuva tieto tarkoittaa EI PISTEYTETTY, ei nollaa.</x:v>
+FI: NYKYJULKAISU: 4 TOIMITTAJAA SEURANNASSA · 1 TOIMITTAJAREITILLÄ SISÄLLÖLLISIÄ VASTAUKSIA · 0 PISTEYTETTY · 0 OSTOVALTUUTTA. Pidä pisteet tyhjinä, kunnes kaikki kuusi pakollista porttia ovat PASS-tilassa. Puuttuva tieto tarkoittaa EI PISTEYTETTY, ei nollaa.</x:v>
       </x:c>
       <x:c r="B5" s="178"/>
       <x:c r="C5" s="178"/>
@@ -4367,8 +4367,8 @@
         <x:v>Passport Nicotine / e-vapour country series</x:v>
       </x:c>
       <x:c r="D15" s="81" t="str">
-        <x:v>WRITTEN RESPONSE + BROCHURE RECEIVED · MULTI-OPTION QUOTE + NUMERICAL SAMPLE REQUEST SENT · RESPONSE PENDING
-FI: KIRJALLINEN VASTAUS + ESITE SAATU · MONIVAIHTOEHTOINEN TARJOUS + NUMEERINEN NÄYTE PYYDETTY · VASTAUS ODOTTAA</x:v>
+        <x:v>TWO WRITTEN RESPONSES + BROCHURE RECEIVED · GERMANY SAMPLE + PRICING PENDING · ROLE/ACCESS CLARIFICATION PENDING · NOT SENT
+FI: KAKSI KIRJALLISTA VASTAUSTA + ESITE SAATU · SAKSA-NÄYTE + HINNOITTELU ODOTTAVAT · ROOLI-/KÄYTTÖMALLIN TÄSMENNYS ODOTTAA · EI LÄHETETTY</x:v>
       </x:c>
       <x:c r="E15" s="192" t="str">
         <x:v>OPEN</x:v>
@@ -4416,7 +4416,7 @@
         <x:v>https://www.euromonitor.com/smokeless-tobacco-e-vapour-products-and-heated-tobacco-in-denmark/report</x:v>
       </x:c>
       <x:c r="X15" s="81" t="str">
-        <x:v>Status only. A follow-up requesting a multi-option quote and numerical sample was sent. The 8-page brochure documents an overall 100-country Passport Tobacco list, not verified e-vapour product-country coverage, plus e-vapour taxonomy and series periods. The numerical sample, itemised price, detailed method, licence terms and verified e-vapour product-country coverage remain pending. No usable data, purchase or commitment.</x:v>
+        <x:v>Status only. Euromonitor says it can provide samples, detailed answers and pricing after the role/access model is clarified. The role/access clarification is pending and has not been sent. The brochure and vendor statement about expanded granularity are not numerical market evidence. The Germany sample, written brand confirmation, itemised price, detailed method, coverage, licence and written derived-output rights remain pending. No usable data, purchase, fee or commitment.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="84" customHeight="1">

--- a/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
+++ b/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="R6754c2daa8c8400a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="R1d336904d8984832"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R26c4b43fcc484d44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="Rdc07a01ec4654730"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R535c176df1d84bf6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="R654d681a94484298"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="R50ffb1cc01184466"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="Rf382c8cd378e46b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="R2e6f1e22e254401e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="Ra30f75fbe70a427a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R0ff77548d6374e9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="R7a26a0dd85074c87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R62209e1706af4907"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="Re0aa331948f24ee9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="R4f55560cb11b40df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R90d88226f30b4dba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1670,7 +1670,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcd1ad43f84c048f7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc7254a43e42145c3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1932,7 +1932,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>Independent decision support · No purchase authorised · Version 2026.07.24-20 · Verified 2026-07-24</x:v>
+        <x:v>Independent decision support · No purchase authorised · Version 2026.07.24-21 · Verified 2026-07-24</x:v>
       </x:c>
       <x:c r="B3" s="9"/>
       <x:c r="C3" s="9"/>
@@ -2421,7 +2421,7 @@
     <x:mergeCell ref="A38:C39"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28bb7e5b6b554ff5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72ea48e0b65b40fa"/>
 </x:worksheet>
 </file>
 
@@ -4367,8 +4367,8 @@
         <x:v>Passport Nicotine / e-vapour country series</x:v>
       </x:c>
       <x:c r="D15" s="81" t="str">
-        <x:v>TWO WRITTEN RESPONSES + BROCHURE RECEIVED · GERMANY SAMPLE + PRICING PENDING · ROLE/ACCESS CLARIFICATION PENDING · NOT SENT
-FI: KAKSI KIRJALLISTA VASTAUSTA + ESITE SAATU · SAKSA-NÄYTE + HINNOITTELU ODOTTAVAT · ROOLI-/KÄYTTÖMALLIN TÄSMENNYS ODOTTAA · EI LÄHETETTY</x:v>
+        <x:v>TWO WRITTEN RESPONSES + BROCHURE RECEIVED · ROLE/ACCESS CLARIFICATION SENT · GERMANY SAMPLE + PRICING PENDING
+FI: KAKSI KIRJALLISTA VASTAUSTA + ESITE SAATU · ROOLI-/KÄYTTÖMALLIN TÄSMENNYS LÄHETETTY · SAKSA-NÄYTE + HINNOITTELU ODOTTAVAT</x:v>
       </x:c>
       <x:c r="E15" s="192" t="str">
         <x:v>OPEN</x:v>
@@ -4416,7 +4416,7 @@
         <x:v>https://www.euromonitor.com/smokeless-tobacco-e-vapour-products-and-heated-tobacco-in-denmark/report</x:v>
       </x:c>
       <x:c r="X15" s="81" t="str">
-        <x:v>Status only. Euromonitor says it can provide samples, detailed answers and pricing after the role/access model is clarified. The role/access clarification is pending and has not been sent. The brochure and vendor statement about expanded granularity are not numerical market evidence. The Germany sample, written brand confirmation, itemised price, detailed method, coverage, licence and written derived-output rights remain pending. No usable data, purchase, fee or commitment.</x:v>
+        <x:v>Status only. Euromonitor says it can provide samples, detailed answers and pricing after the role/access model is clarified. A role/access clarification was sent on 2026-07-24. The brochure and vendor statement about expanded granularity are not numerical market evidence. The Germany sample, written brand confirmation, itemised price, detailed method, country-product coverage matrix, licence and written derived-output rights remain pending. No usable data, score, purchase, fee or commitment.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="84" customHeight="1">

--- a/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
+++ b/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="R2e6f1e22e254401e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="Ra30f75fbe70a427a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R0ff77548d6374e9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="R7a26a0dd85074c87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R62209e1706af4907"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="Re0aa331948f24ee9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="R4f55560cb11b40df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R90d88226f30b4dba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="R61fb5a9412b1451f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="Rcdc99d7374a34e9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="Ra512bb80c1d347bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="Ra0a38ee276fe40e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="Rf66f78ba17c64fcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="Recf7dd430d294be1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="Rcb53607f9eef4bf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R572ee0d3d5e14ae3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1670,7 +1670,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc7254a43e42145c3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R51751ff97fae43e0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1932,7 +1932,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>Independent decision support · No purchase authorised · Version 2026.07.24-21 · Verified 2026-07-24</x:v>
+        <x:v>Independent decision support · No purchase authorised · Version 2026.07.25-24 · Verified 2026-07-25</x:v>
       </x:c>
       <x:c r="B3" s="9"/>
       <x:c r="C3" s="9"/>
@@ -2030,8 +2030,8 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="59" t="str">
-        <x:v>1) Request samples and transaction-use quotes from ECigIntelligence and Euromonitor in parallel. 2) Buy at most one global master. Default to ECigIntelligence at USD 3,995 if its sample and licence pass; choose Euromonitor only if its quote demonstrates enough additional institutional and country coverage. 3) Add a tightly scoped NIQ/Circana POS pilot only as a validation layer for Germany, the United States and the United Kingdom.
-FI: 1) Pyydä näytteet ja transaktiokäyttötarjoukset rinnakkain ECigIntelligenceltä ja Euromonitorilta. 2) Osta enintään yksi globaali pääaineisto. Oletusvalinta on ECigIntelligence hintaan 3 995 USD, jos näyte ja lisenssi läpäisevät ehdot; valitse Euromonitor vain, jos tarjous osoittaa riittävän lisäarvon institutionaalisessa ja maapeitossa. 3) Lisää rajattu NIQ/Circana-POS-pilotti vain varmennuskerrokseksi Saksaan, Yhdysvaltoihin ja Britanniaan.</x:v>
+        <x:v>1) Continue sample and transaction-rights evaluation with ECigIntelligence and Euromonitor in parallel. 2) Buy at most one global master. Do not buy Euromonitor before a full Germany sample, exact coverage matrix, category-specific method and written Pixan, lender, buyer, adviser, data-room and audit-archive rights pass review. 3) Add a tightly scoped NIQ/Circana POS pilot only as a validation layer for Germany, the United States and the United Kingdom.
+FI: 1) Jatka ECigIntelligencen ja Euromonitorin näyte- ja transaktio-oikeuksien arviointia rinnakkain. 2) Osta enintään yksi globaali pääaineisto. Älä osta Euromonitoria ennen kuin täysi Saksa-näyte, täsmällinen peittomatriisi, kategoriakohtainen menetelmä sekä kirjalliset Pixan-, lainanantaja-, ostaja-, neuvonantaja-, datahuone- ja tarkastusarkisto-oikeudet läpäisevät tarkistuksen. 3) Lisää rajattu NIQ/Circana-POS-pilotti vain varmennuskerrokseksi Saksaan, Yhdysvaltoihin ja Britanniaan.</x:v>
       </x:c>
       <x:c r="B10" s="60"/>
       <x:c r="C10" s="60"/>
@@ -2179,12 +2179,12 @@
       <x:c r="K17" s="94"/>
       <x:c r="L17" s="94"/>
       <x:c r="M17" s="94" t="str">
-        <x:v>USD 3,995 or vendor quote + POS quote</x:v>
+        <x:v>USD 3,995 or private indicative Euromonitor quote + POS quote</x:v>
       </x:c>
       <x:c r="N17" s="94"/>
       <x:c r="O17" s="94" t="str">
-        <x:v>Euromonitor and POS prices, users, exports and transaction rights.
-FI: Euromonitorin ja POS-aineiston hinnat, käyttäjät, viennit ja transaktio-oikeudet.</x:v>
+        <x:v>Final Euromonitor scope, VAT, exact country list, exports, Pixan onward sharing and transaction rights; POS price.
+FI: Euromonitorin lopullinen laajuus, ALV, täsmällinen maalista, viennit, Pixanin edelleenjakelu ja transaktio-oikeudet; POS-hinta.</x:v>
       </x:c>
       <x:c r="P17" s="94"/>
     </x:row>
@@ -2421,7 +2421,7 @@
     <x:mergeCell ref="A38:C39"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72ea48e0b65b40fa"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d939d97bc874d70"/>
 </x:worksheet>
 </file>
 
@@ -2624,11 +2624,13 @@
         <x:v>core_global_choose_one</x:v>
       </x:c>
       <x:c r="F7" s="132" t="str">
-        <x:v>Quote; Denmark single-country example USD 1,195</x:v>
+        <x:v>Private indicative annual quotes received</x:v>
       </x:c>
       <x:c r="G7" s="132" t="str">
-        <x:v>Request a Passport Nicotine quote and sample Excel in parallel with ECigIntelligence, then buy at most one global master unless non-overlap is demonstrated.
-FI: Pyydä Passport Nicotine -tarjous ja näyte-Excel rinnakkain ECigIntelligencen kanssa; osta enintään yksi globaali pääaineisto, ellei päällekkäisyyden puuttumista osoiteta.</x:v>
+        <x:v>Continue evaluation, but do not buy before a full 2022–2025 Germany sample, exact country-product matrix, category-specific method and written Pixan, lender, buyer, adviser, data-room and audit-archive rights are confirmed. Buy at most one global master unless non-overlap is demonstrated.
+The received Germany sample proves field structure but is too sparse for the official 2023–2024 liquid-volume reconciliation. The methodology is generic, the exact e-vapour coverage matrix is missing and the default licence does not yet fit the intended onward-sharing, data-room, public or legal-use workflow. No licensed values are published.
+FI: Jatka arviointia, mutta älä osta ennen kuin täysi Saksan 2022–2025-näyte, täsmällinen maa–tuote-matriisi, kategoriakohtainen menetelmä sekä kirjalliset Pixan-, lainanantaja-, ostaja-, neuvonantaja-, datahuone- ja tarkastusarkisto-oikeudet on vahvistettu. Osta enintään yksi globaali pääaineisto, ellei päällekkäisyyden puuttumista osoiteta.
+Saatu Saksa-näyte osoittaa kenttärakenteen, mutta on liian suppea vuosien 2023–2024 viralliseen nestemäärätäsmäytykseen. Menetelmä on yleinen, täsmällinen sähkötupakan peittomatriisi puuttuu eikä vakiolisenssi vielä sovi aiottuun edelleenjakelu-, datahuone-, julkiseen tai oikeudelliseen käyttöön. Lisensoituja arvoja ei julkaista.</x:v>
       </x:c>
       <x:c r="H7" s="133" t="n">
         <x:v>4</x:v>
@@ -4367,8 +4369,8 @@
         <x:v>Passport Nicotine / e-vapour country series</x:v>
       </x:c>
       <x:c r="D15" s="81" t="str">
-        <x:v>TWO WRITTEN RESPONSES + BROCHURE RECEIVED · ROLE/ACCESS CLARIFICATION SENT · GERMANY SAMPLE + PRICING PENDING
-FI: KAKSI KIRJALLISTA VASTAUSTA + ESITE SAATU · ROOLI-/KÄYTTÖMALLIN TÄSMENNYS LÄHETETTY · SAKSA-NÄYTE + HINNOITTELU ODOTTAVAT</x:v>
+        <x:v>GERMANY SAMPLE + METHOD + TWO QUOTES RECEIVED · 0/6 GATES PASS · NOT SCORED
+FI: SAKSA-NÄYTE + MENETELMÄ + KAKSI TARJOUSTA SAATU · 0/6 PORTTIA LÄPÄISTY · EI PISTEYTETTY</x:v>
       </x:c>
       <x:c r="E15" s="192" t="str">
         <x:v>OPEN</x:v>
@@ -4416,7 +4418,7 @@
         <x:v>https://www.euromonitor.com/smokeless-tobacco-e-vapour-products-and-heated-tobacco-in-denmark/report</x:v>
       </x:c>
       <x:c r="X15" s="81" t="str">
-        <x:v>Status only. Euromonitor says it can provide samples, detailed answers and pricing after the role/access model is clarified. A role/access clarification was sent on 2026-07-24. The brochure and vendor statement about expanded granularity are not numerical market evidence. The Germany sample, written brand confirmation, itemised price, detailed method, country-product coverage matrix, licence and written derived-output rights remain pending. No usable data, score, purchase, fee or commitment.</x:v>
+        <x:v>Status only. A sparse Germany sample, generic methodology and two indicative quotes were received. The workbook does not satisfy the representative-sample gate; all six mandatory gates remain OPEN. No licensed values are published. NOT SCORED; no purchase, fee or commitment.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="84" customHeight="1">

--- a/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
+++ b/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="R61fb5a9412b1451f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="Rcdc99d7374a34e9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="Ra512bb80c1d347bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="Ra0a38ee276fe40e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="Rf66f78ba17c64fcd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="Recf7dd430d294be1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="Rcb53607f9eef4bf1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R572ee0d3d5e14ae3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="Rd9eddb0b918146fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="R3b66e84e67784eab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R4c9ae2cb4eef437a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="R37e309393bef4327"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R0d54d505c2d049fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="Rce79ac95bebe4a99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="R53515f0745fd40fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R561ea5e767f64190"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1670,7 +1670,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R51751ff97fae43e0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R15efe3e934594909"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1932,7 +1932,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>Independent decision support · No purchase authorised · Version 2026.07.25-24 · Verified 2026-07-25</x:v>
+        <x:v>Independent decision support · No purchase authorised · Version 2026.07.27-30 · Verified 2026-07-27</x:v>
       </x:c>
       <x:c r="B3" s="9"/>
       <x:c r="C3" s="9"/>
@@ -2030,8 +2030,8 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="59" t="str">
-        <x:v>1) Continue sample and transaction-rights evaluation with ECigIntelligence and Euromonitor in parallel. 2) Buy at most one global master. Do not buy Euromonitor before a full Germany sample, exact coverage matrix, category-specific method and written Pixan, lender, buyer, adviser, data-room and audit-archive rights pass review. 3) Add a tightly scoped NIQ/Circana POS pilot only as a validation layer for Germany, the United States and the United Kingdom.
-FI: 1) Jatka ECigIntelligencen ja Euromonitorin näyte- ja transaktio-oikeuksien arviointia rinnakkain. 2) Osta enintään yksi globaali pääaineisto. Älä osta Euromonitoria ennen kuin täysi Saksa-näyte, täsmällinen peittomatriisi, kategoriakohtainen menetelmä sekä kirjalliset Pixan-, lainanantaja-, ostaja-, neuvonantaja-, datahuone- ja tarkastusarkisto-oikeudet läpäisevät tarkistuksen. 3) Lisää rajattu NIQ/Circana-POS-pilotti vain varmennuskerrokseksi Saksaan, Yhdysvaltoihin ja Britanniaan.</x:v>
+        <x:v>1) Continue sample and transaction-rights evaluation with ECigIntelligence and Euromonitor in parallel. 2) Buy at most one global master; do not buy before a populated 2022–2025 Germany test, reconciled 78/95 country-product-field-year coverage, record-level status flags, a legally approved NDA data-room Special Condition and complete all-in commercial terms pass review. 3) Consider a tightly scoped NIQ/Circana POS pilot only as a later validation layer for selected countries.
+FI: 1) Jatka ECigIntelligencen ja Euromonitorin näyte- ja transaktio-oikeuksien arviointia rinnakkain. 2) Osta enintään yksi globaali pääaineisto; älä osta ennen kuin täytetty Saksan 2022–2025-testi, täsmäytetty 78/95 maan maa–tuote–kenttä–vuosi-peitto, tietuetason tilamerkinnät, legal-tiimin hyväksymä NDA-datahuone-erityisehto ja täydelliset kaikki kustannukset kattavat kaupalliset ehdot läpäisevät tarkistuksen. 3) Harkitse rajattua NIQ/Circana-POS-pilottia vasta myöhempänä varmennuskerroksena valituille maille.</x:v>
       </x:c>
       <x:c r="B10" s="60"/>
       <x:c r="C10" s="60"/>
@@ -2421,7 +2421,7 @@
     <x:mergeCell ref="A38:C39"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d939d97bc874d70"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9603de3d86184d3f"/>
 </x:worksheet>
 </file>
 
@@ -2607,7 +2607,7 @@
         <x:v>https://ecigintelligence.com/product-category/premium-data-bundles/</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="78" customHeight="1">
+    <x:row r="7" ht="270" customHeight="1">
       <x:c r="A7" s="131" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -2627,10 +2627,10 @@
         <x:v>Private indicative annual quotes received</x:v>
       </x:c>
       <x:c r="G7" s="132" t="str">
-        <x:v>Continue evaluation, but do not buy before a full 2022–2025 Germany sample, exact country-product matrix, category-specific method and written Pixan, lender, buyer, adviser, data-room and audit-archive rights are confirmed. Buy at most one global master unless non-overlap is demonstrated.
-The received Germany sample proves field structure but is too sparse for the official 2023–2024 liquid-volume reconciliation. The methodology is generic, the exact e-vapour coverage matrix is missing and the default licence does not yet fit the intended onward-sharing, data-room, public or legal-use workflow. No licensed values are published.
-FI: Jatka arviointia, mutta älä osta ennen kuin täysi Saksan 2022–2025-näyte, täsmällinen maa–tuote-matriisi, kategoriakohtainen menetelmä sekä kirjalliset Pixan-, lainanantaja-, ostaja-, neuvonantaja-, datahuone- ja tarkastusarkisto-oikeudet on vahvistettu. Osta enintään yksi globaali pääaineisto, ellei päällekkäisyyden puuttumista osoiteta.
-Saatu Saksa-näyte osoittaa kenttärakenteen, mutta on liian suppea vuosien 2023–2024 viralliseen nestemäärätäsmäytykseen. Menetelmä on yleinen, täsmällinen sähkötupakan peittomatriisi puuttuu eikä vakiolisenssi vielä sovi aiottuun edelleenjakelu-, datahuone-, julkiseen tai oikeudelliseen käyttöön. Lisensoituja arvoja ei julkaista.</x:v>
+        <x:v>Continue evaluation, but do not buy before a populated 2022–2025 Germany test, reconciled 78/95 country-product-field-year coverage, category-specific method and record-status flags, a legally approved Pixan/NDA data-room Special Condition, and complete all-in commercial terms are confirmed. Buy at most one global master unless non-overlap is demonstrated.
+The expanded Germany sample permits a private 2023–2024 numerical liquid-volume comparison, but the later 95-geography schema workbook has blank country-year value cells. End-consumer tax basis, restricted enterprise-AI processing and modelled Cyprus volume were clarified; observed/reported/modelled record flags, the exact product bridge, NDA data-room rights, export and retention rights, taxes, fees and renewal terms remain open. No licensed values or private quote amounts are published.
+FI: Jatka arviointia, mutta älä osta ennen kuin täytetty Saksan 2022–2025-testi, täsmäytetty 78/95 maan maa–tuote–kenttä–vuosi-peitto, kategoriakohtainen menetelmä ja tietueiden tilamerkinnät, legal-tiimin hyväksymä Pixan-/NDA-datahuone-erityisehto sekä täydelliset kaikki kustannukset kattavat kaupalliset ehdot on vahvistettu. Osta enintään yksi globaali pääaineisto, ellei päällekkäisyyden puuttumista osoiteta.
+Laajennettu Saksa-näyte mahdollistaa yksityisen vuosien 2023–2024 numeerisen nestemäärävertailun, mutta myöhemmän 95 maantieteen skeematyökirjan maa–vuosi-arvosolut ovat tyhjiä. Loppuasiakasmyynnin veroperusta, rajattu yritystason tekoälykäsittely ja mallinnettu Kyproksen volyymi täsmennettiin; havaittu/raportoitu/mallinnettu-tietuemerkinnät, täsmällinen tuotesilta, NDA-datahuoneoikeudet, vienti- ja säilytysoikeudet, verot, maksut ja uusimisehdot ovat avoinna. Lisensoituja arvoja tai yksityisiä tarjoushintoja ei julkaista.</x:v>
       </x:c>
       <x:c r="H7" s="133" t="n">
         <x:v>4</x:v>
@@ -4369,8 +4369,8 @@
         <x:v>Passport Nicotine / e-vapour country series</x:v>
       </x:c>
       <x:c r="D15" s="81" t="str">
-        <x:v>GERMANY SAMPLE + METHOD + TWO QUOTES RECEIVED · 0/6 GATES PASS · NOT SCORED
-FI: SAKSA-NÄYTE + MENETELMÄ + KAKSI TARJOUSTA SAATU · 0/6 PORTTIA LÄPÄISTY · EI PISTEYTETTY</x:v>
+        <x:v>EXPANDED SAMPLE + 78-MARKET LIST + 95-GEOGRAPHY SCHEMA + THREE QUOTES RECEIVED · 0/6 GATES PASS · NOT SCORED
+FI: LAAJENNETTU NÄYTE + 78 MARKKINAN LISTA + 95 MAANTIETEEN SKEEMA + KOLME TARJOUSTA SAATU · 0/6 PORTTIA LÄPÄISTY · EI PISTEYTETTY</x:v>
       </x:c>
       <x:c r="E15" s="192" t="str">
         <x:v>OPEN</x:v>
@@ -4418,7 +4418,7 @@
         <x:v>https://www.euromonitor.com/smokeless-tobacco-e-vapour-products-and-heated-tobacco-in-denmark/report</x:v>
       </x:c>
       <x:c r="X15" s="81" t="str">
-        <x:v>Status only. A sparse Germany sample, generic methodology and two indicative quotes were received. The workbook does not satisfy the representative-sample gate; all six mandatory gates remain OPEN. No licensed values are published. NOT SCORED; no purchase, fee or commitment.</x:v>
+        <x:v>Status only. An expanded Germany sample, 78-market list, generic methodology, standard terms, three indicative quotes and a later blank-value 95-geography schema were received. All six mandatory gates remain OPEN. No licensed values or private quote amounts are published. NOT SCORED; no purchase, fee or commitment.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="84" customHeight="1">

--- a/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
+++ b/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="Rd9eddb0b918146fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="R3b66e84e67784eab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R4c9ae2cb4eef437a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="R37e309393bef4327"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R0d54d505c2d049fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="Rce79ac95bebe4a99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="R53515f0745fd40fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R561ea5e767f64190"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="Rf8dd5b7b9601442a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="Racfb30560ef841de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R39aebe452a6a417f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="R0b9e371b8c444f5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R9b51127cd6054b27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="R41f2f4448c884d4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="R6d4b6fb1ceb14f1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R211c57bc433e4469"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1670,7 +1670,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R15efe3e934594909"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R17944193765a4c5d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1932,7 +1932,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>Independent decision support · No purchase authorised · Version 2026.07.27-30 · Verified 2026-07-27</x:v>
+        <x:v>Independent decision support · No purchase authorised · Version 2026.07.28-32 · Verified 2026-07-28</x:v>
       </x:c>
       <x:c r="B3" s="9"/>
       <x:c r="C3" s="9"/>
@@ -2421,7 +2421,7 @@
     <x:mergeCell ref="A38:C39"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9603de3d86184d3f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67dbb9ad67914177"/>
 </x:worksheet>
 </file>
 
@@ -4306,8 +4306,8 @@
         <x:v>Global Market Database</x:v>
       </x:c>
       <x:c r="D14" s="80" t="str">
-        <x:v>REQUEST SENT · NO RESPONSE OR AUTO-ACK · FOLLOW-UP 2026-07-28
-FI: PYYNTÖ LÄHETETTY · EI VASTAUSTA TAI AUTOMAATTIKUITTAUSTA · SEURANTA 2026-07-28</x:v>
+        <x:v>REQUEST + FOLLOW-UP SENT · RESPONSE PENDING · NOT SCORED
+FI: PYYNTÖ + SEURANTA LÄHETETTY · VASTAUS ODOTTAA · EI PISTEYTETTY</x:v>
       </x:c>
       <x:c r="E14" s="191" t="str">
         <x:v>OPEN</x:v>
@@ -4355,7 +4355,7 @@
         <x:v>https://ecigintelligence.com/product-category/premium-data-bundles/</x:v>
       </x:c>
       <x:c r="X14" s="80" t="str">
-        <x:v>Status only. Request sent 2026-07-23; no bounce, automated acknowledgement, response content or unlicensed data. First follow-up due 2026-07-28 if unanswered.</x:v>
+        <x:v>Status only. Request sent 2026-07-23 and first follow-up sent 2026-07-28. No response, sample, quote, data, method, coverage, licence, price or commitment is recorded. NOT SCORED; no purchase is authorised.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="84" customHeight="1">
@@ -4495,8 +4495,8 @@
         <x:v>US Tobacco POS pilot</x:v>
       </x:c>
       <x:c r="D17" s="81" t="str">
-        <x:v>SUBMISSION CONFIRMED · RESPONSE PENDING
-FI: LÄHETYS VAHVISTETTU · VASTAUS ODOTTAA</x:v>
+        <x:v>FOLLOW-UP SENT 2026-07-28 · SAMPLE + QUOTE PENDING · NOT SCORED
+FI: SEURANTA LÄHETETTY 28.7.2026 · NÄYTE + TARJOUS ODOTTAVAT · EI PISTEYTETTY</x:v>
       </x:c>
       <x:c r="E17" s="192" t="str">
         <x:v>OPEN</x:v>
@@ -4544,7 +4544,7 @@
         <x:v>https://www.circana.com/industries/tobacco</x:v>
       </x:c>
       <x:c r="X17" s="81" t="str">
-        <x:v>Status only. No response content or unlicensed data.</x:v>
+        <x:v>Status only. A direct follow-up requested a United States retail sample, channel and method details, a non-binding minimum configuration and transaction-use rights. A substantive sample and quote remain pending. NOT SCORED; no purchase or other commitment is authorised.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">

--- a/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
+++ b/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="Rf8dd5b7b9601442a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="Racfb30560ef841de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R39aebe452a6a417f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="R0b9e371b8c444f5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R9b51127cd6054b27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="R41f2f4448c884d4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="R6d4b6fb1ceb14f1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R211c57bc433e4469"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="Rc014e37b7cac42cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="Rf513e51abc9141ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R9d5326605f204ee4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="R8dfdda350c2444e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R42c20f5b1fbc4859"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="R6e6a894906ea4bb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="R3b6cc9456e864022"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R7ac251809cc44673"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1670,7 +1670,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R17944193765a4c5d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1eb8d78e134d468e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1932,7 +1932,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>Independent decision support · No purchase authorised · Version 2026.07.28-32 · Verified 2026-07-28</x:v>
+        <x:v>Independent decision support · No purchase authorised · Version 2026.07.29-35 · Verified 2026-07-29</x:v>
       </x:c>
       <x:c r="B3" s="9"/>
       <x:c r="C3" s="9"/>
@@ -2030,8 +2030,8 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="59" t="str">
-        <x:v>1) Continue sample and transaction-rights evaluation with ECigIntelligence and Euromonitor in parallel. 2) Buy at most one global master; do not buy before a populated 2022–2025 Germany test, reconciled 78/95 country-product-field-year coverage, record-level status flags, a legally approved NDA data-room Special Condition and complete all-in commercial terms pass review. 3) Consider a tightly scoped NIQ/Circana POS pilot only as a later validation layer for selected countries.
-FI: 1) Jatka ECigIntelligencen ja Euromonitorin näyte- ja transaktio-oikeuksien arviointia rinnakkain. 2) Osta enintään yksi globaali pääaineisto; älä osta ennen kuin täytetty Saksan 2022–2025-testi, täsmäytetty 78/95 maan maa–tuote–kenttä–vuosi-peitto, tietuetason tilamerkinnät, legal-tiimin hyväksymä NDA-datahuone-erityisehto ja täydelliset kaikki kustannukset kattavat kaupalliset ehdot läpäisevät tarkistuksen. 3) Harkitse rajattua NIQ/Circana-POS-pilottia vasta myöhempänä varmennuskerroksena valituille maille.</x:v>
+        <x:v>1) Continue sample and transaction-rights evaluation with ECigIntelligence and Euromonitor in parallel. 2) Do not activate the conditional Germany extract or buy before explicit purchase authority, a populated current 2022–2025 Germany test, reconciled 78/95 country-product-field-year coverage, record-level status flags, a legally approved NDA data-room Special Condition and complete all-in commercial terms pass review. 3) Consider a tightly scoped NIQ/Circana POS pilot only as a later validation layer for selected countries.
+FI: 1) Jatka ECigIntelligencen ja Euromonitorin näyte- ja transaktio-oikeuksien arviointia rinnakkain. 2) Älä aktivoi ehdollista Saksa-otetta tai osta ennen nimenomaista ostovaltuutusta, täytettyä ajantasaista Saksan 2022–2025-testiä, täsmäytettyä 78/95 maan maa–tuote–kenttä–vuosi-peittoa, tietuetason tilamerkinnät, legal-tiimin hyväksymä NDA-datahuone-erityisehto ja täydelliset kaikki kustannukset kattavat kaupalliset ehdot läpäisevät tarkistuksen. 3) Harkitse rajattua NIQ/Circana-POS-pilottia vasta myöhempänä varmennuskerroksena valituille maille.</x:v>
       </x:c>
       <x:c r="B10" s="60"/>
       <x:c r="C10" s="60"/>
@@ -2421,7 +2421,7 @@
     <x:mergeCell ref="A38:C39"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67dbb9ad67914177"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7fb5192883c435e"/>
 </x:worksheet>
 </file>
 
@@ -2627,10 +2627,10 @@
         <x:v>Private indicative annual quotes received</x:v>
       </x:c>
       <x:c r="G7" s="132" t="str">
-        <x:v>Continue evaluation, but do not buy before a populated 2022–2025 Germany test, reconciled 78/95 country-product-field-year coverage, category-specific method and record-status flags, a legally approved Pixan/NDA data-room Special Condition, and complete all-in commercial terms are confirmed. Buy at most one global master unless non-overlap is demonstrated.
-The expanded Germany sample permits a private 2023–2024 numerical liquid-volume comparison, but the later 95-geography schema workbook has blank country-year value cells. End-consumer tax basis, restricted enterprise-AI processing and modelled Cyprus volume were clarified; observed/reported/modelled record flags, the exact product bridge, NDA data-room rights, export and retention rights, taxes, fees and renewal terms remain open. No licensed values or private quote amounts are published.
-FI: Jatka arviointia, mutta älä osta ennen kuin täytetty Saksan 2022–2025-testi, täsmäytetty 78/95 maan maa–tuote–kenttä–vuosi-peitto, kategoriakohtainen menetelmä ja tietueiden tilamerkinnät, legal-tiimin hyväksymä Pixan-/NDA-datahuone-erityisehto sekä täydelliset kaikki kustannukset kattavat kaupalliset ehdot on vahvistettu. Osta enintään yksi globaali pääaineisto, ellei päällekkäisyyden puuttumista osoiteta.
-Laajennettu Saksa-näyte mahdollistaa yksityisen vuosien 2023–2024 numeerisen nestemäärävertailun, mutta myöhemmän 95 maantieteen skeematyökirjan maa–vuosi-arvosolut ovat tyhjiä. Loppuasiakasmyynnin veroperusta, rajattu yritystason tekoälykäsittely ja mallinnettu Kyproksen volyymi täsmennettiin; havaittu/raportoitu/mallinnettu-tietuemerkinnät, täsmällinen tuotesilta, NDA-datahuoneoikeudet, vienti- ja säilytysoikeudet, verot, maksut ja uusimisehdot ovat avoinna. Lisensoituja arvoja tai yksityisiä tarjoushintoja ei julkaista.</x:v>
+        <x:v>Continue evaluation, but do not activate the conditional Germany extract or buy before explicit purchase authority and a populated current 2022–2025 Germany test, reconciled 78/95 country-product-field-year coverage, category-specific method and record-status flags, a legally approved Pixan/NDA data-room Special Condition, and complete all-in commercial terms are confirmed. Buy at most one global master unless non-overlap is demonstrated.
+The expanded Germany sample permits a private 2023–2024 numerical liquid-volume comparison, but the product scope, retail-versus-tax stage and record-status bridge remain unresolved and the later 95-geography schema workbook has blank country-year value cells. A conditional paid Germany extract was offered on 2026-07-29; it has not been accepted or activated. End-consumer tax basis, restricted enterprise-AI processing and modelled Cyprus volume were clarified; NDA data-room rights, export and retention rights, taxes, fees and renewal terms remain open. No licensed values or private quote amounts are published.
+FI: Jatka arviointia, mutta älä aktivoi ehdollista Saksa-otetta tai osta ennen nimenomaista ostovaltuutusta ja ennen kuin täytetty ajantasainen Saksan 2022–2025-testi, täsmäytetty 78/95 maan maa–tuote–kenttä–vuosi-peitto, kategoriakohtainen menetelmä ja tietueiden tilamerkinnät, legal-tiimin hyväksymä Pixan-/NDA-datahuone-erityisehto sekä täydelliset kaikki kustannukset kattavat kaupalliset ehdot on vahvistettu. Osta enintään yksi globaali pääaineisto, ellei päällekkäisyyden puuttumista osoiteta.
+Laajennettu Saksa-näyte mahdollistaa yksityisen vuosien 2023–2024 numeerisen nestemäärävertailun, mutta tuoterajaus, vähittäis- ja verovaiheen ero sekä tietueiden tilasilta ovat ratkaisematta ja myöhemmän 95 maantieteen skeematyökirjan maa–vuosi-arvosolut ovat tyhjiä. Ehdollinen maksullinen Saksa-ote tarjottiin 29.7.2026; sitä ei ole hyväksytty tai aktivoitu. Loppuasiakasmyynnin veroperusta, rajattu yritystason tekoälykäsittely ja mallinnettu Kyproksen volyymi täsmennettiin; NDA-datahuoneoikeudet, vienti- ja säilytysoikeudet, verot, maksut ja uusimisehdot ovat avoinna. Lisensoituja arvoja tai yksityisiä tarjoushintoja ei julkaista.</x:v>
       </x:c>
       <x:c r="H7" s="133" t="n">
         <x:v>4</x:v>
@@ -4369,8 +4369,8 @@
         <x:v>Passport Nicotine / e-vapour country series</x:v>
       </x:c>
       <x:c r="D15" s="81" t="str">
-        <x:v>EXPANDED SAMPLE + 78-MARKET LIST + 95-GEOGRAPHY SCHEMA + THREE QUOTES RECEIVED · 0/6 GATES PASS · NOT SCORED
-FI: LAAJENNETTU NÄYTE + 78 MARKKINAN LISTA + 95 MAANTIETEEN SKEEMA + KOLME TARJOUSTA SAATU · 0/6 PORTTIA LÄPÄISTY · EI PISTEYTETTY</x:v>
+        <x:v>CALL COMPLETED + CONDITIONAL PAID GERMANY EXTRACT OFFERED · NOT ACCEPTED · 0/6 GATES PASS · NOT SCORED
+FI: PUHELU PIDETTY + EHDOLLINEN MAKSULLINEN SAKSA-OTE TARJOTTU · EI HYVÄKSYTTY · 0/6 PORTTIA LÄPÄISTY · EI PISTEYTETTY</x:v>
       </x:c>
       <x:c r="E15" s="192" t="str">
         <x:v>OPEN</x:v>
@@ -4418,7 +4418,7 @@
         <x:v>https://www.euromonitor.com/smokeless-tobacco-e-vapour-products-and-heated-tobacco-in-denmark/report</x:v>
       </x:c>
       <x:c r="X15" s="81" t="str">
-        <x:v>Status only. An expanded Germany sample, 78-market list, generic methodology, standard terms, three indicative quotes and a later blank-value 95-geography schema were received. All six mandatory gates remain OPEN. No licensed values or private quote amounts are published. NOT SCORED; no purchase, fee or commitment.</x:v>
+        <x:v>Status only. A conditional paid Germany extract was offered after the 2026-07-29 call. It has not been accepted or activated; no order, invoice, fee, subscription or commitment is authorised. Product scope, transaction-stage reconciliation, current Germany coverage, rights and all-in terms remain open. NOT SCORED; 0/6 gates pass.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="84" customHeight="1">

--- a/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
+++ b/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="Rc014e37b7cac42cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="Rf513e51abc9141ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R9d5326605f204ee4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="R8dfdda350c2444e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R42c20f5b1fbc4859"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="R6e6a894906ea4bb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="R3b6cc9456e864022"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R7ac251809cc44673"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="Rdf2804040c294db4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="R04be9e45ccb14d06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R1917f8f1f5c34646"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="Ra3a8a1872a51401f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R0496531a64414ea7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="R01c1d8e759fa484b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="R2ee3864ab1584e38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="Re391b33689054e74"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1670,7 +1670,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1eb8d78e134d468e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbd11b4395b234d47"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1932,7 +1932,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>Independent decision support · No purchase authorised · Version 2026.07.29-35 · Verified 2026-07-29</x:v>
+        <x:v>Independent decision support · No purchase authorised · Version 2026.07.30-36 · Verified 2026-07-30</x:v>
       </x:c>
       <x:c r="B3" s="9"/>
       <x:c r="C3" s="9"/>
@@ -2421,7 +2421,7 @@
     <x:mergeCell ref="A38:C39"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7fb5192883c435e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90e1642408d34644"/>
 </x:worksheet>
 </file>
 

--- a/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
+++ b/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="Rdf2804040c294db4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="R04be9e45ccb14d06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R1917f8f1f5c34646"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="Ra3a8a1872a51401f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R0496531a64414ea7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="R01c1d8e759fa484b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="R2ee3864ab1584e38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="Re391b33689054e74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="R46a33ea768654c93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="Rc2323bce54f44a2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R8f927fce62354329"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="Ra37bfa6b87c94aeb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="Ra7bf56130aad4dd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="R07ee227e3b914909"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="R1414de42e70a40ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="Rb80f59d2d8594a98"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1594,9 +1594,6 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="48672768"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="48672768"/>
@@ -1670,7 +1667,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbd11b4395b234d47"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0ca2db5bf9b0433e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1932,7 +1929,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>Independent decision support · No purchase authorised · Version 2026.07.30-36 · Verified 2026-07-30</x:v>
+        <x:v>Independent decision support · No purchase authorised · Version 2026.07.31-37 · Verified 2026-07-31</x:v>
       </x:c>
       <x:c r="B3" s="9"/>
       <x:c r="C3" s="9"/>
@@ -2421,7 +2418,7 @@
     <x:mergeCell ref="A38:C39"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90e1642408d34644"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R413fb7489ddb49e8"/>
 </x:worksheet>
 </file>
 

--- a/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
+++ b/site/downloads/pixan-paid-data-procurement-fi-en.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="R46a33ea768654c93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="Rc2323bce54f44a2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R8f927fce62354329"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="Ra37bfa6b87c94aeb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="Ra7bf56130aad4dd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="R07ee227e3b914909"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="R1414de42e70a40ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="Rb80f59d2d8594a98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision" sheetId="1" r:id="Rb6c572953e7744a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priorities" sheetId="2" r:id="R590f3a33224a40f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFP Gate" sheetId="3" r:id="R5fef77f018d7432f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avoid" sheetId="4" r:id="R22ea87a197714660"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R3d690b15798b4c91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Response Scorecard" sheetId="6" r:id="Rde4b021110de424b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intake Template" sheetId="7" r:id="R61a00756c96e4d0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" r:id="R507a11ff44814aea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1594,6 +1594,9 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="48672768"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="48672768"/>
@@ -1667,7 +1670,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0ca2db5bf9b0433e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2c6ba48b87244ea3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1929,7 +1932,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>Independent decision support · No purchase authorised · Version 2026.07.31-37 · Verified 2026-07-31</x:v>
+        <x:v>Independent decision support · Germany extract delivered · Wider package HOLD · Version 2026.08.03-43 · Verified 2026-08-03</x:v>
       </x:c>
       <x:c r="B3" s="9"/>
       <x:c r="C3" s="9"/>
@@ -1949,9 +1952,9 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="29" t="str">
-        <x:v>DECISION STATUS: NO SPEND AUTHORISED
-Ask Pixan whether it wants to fund the shortlist, but place no order before every sample, method and licence gate is closed.
-PÄÄTÖSTILA: EI OSTOVALTUUTTA. Pixanilta voidaan pyytää rahoituspäätös, mutta tilausta ei tehdä ennen kaikkien näyte-, menetelmä- ja lisenssiporttien sulkemista.</x:v>
+        <x:v>DECISION STATUS: NO WIDER-PACKAGE SPEND AUTHORISED
+The one-country Germany extract was accepted and delivered. Do not place a 25/50/78-country order before the remaining method, scope, rights and commercial gates are closed.
+PÄÄTÖSTILA: LAAJEMMAN PAKETIN OSTOVALTUUTTA EI OLE. Yhden maan Saksa-ote hyväksyttiin ja toimitettiin. Älä tilaa 25/50/78 maan pakettia ennen jäljellä olevien menetelmä-, rajaus-, käyttöoikeus- ja kaupallisten porttien sulkemista.</x:v>
       </x:c>
       <x:c r="B5" s="30"/>
       <x:c r="C5" s="30"/>
@@ -2027,8 +2030,8 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="59" t="str">
-        <x:v>1) Continue sample and transaction-rights evaluation with ECigIntelligence and Euromonitor in parallel. 2) Do not activate the conditional Germany extract or buy before explicit purchase authority, a populated current 2022–2025 Germany test, reconciled 78/95 country-product-field-year coverage, record-level status flags, a legally approved NDA data-room Special Condition and complete all-in commercial terms pass review. 3) Consider a tightly scoped NIQ/Circana POS pilot only as a later validation layer for selected countries.
-FI: 1) Jatka ECigIntelligencen ja Euromonitorin näyte- ja transaktio-oikeuksien arviointia rinnakkain. 2) Älä aktivoi ehdollista Saksa-otetta tai osta ennen nimenomaista ostovaltuutusta, täytettyä ajantasaista Saksan 2022–2025-testiä, täsmäytettyä 78/95 maan maa–tuote–kenttä–vuosi-peittoa, tietuetason tilamerkinnät, legal-tiimin hyväksymä NDA-datahuone-erityisehto ja täydelliset kaikki kustannukset kattavat kaupalliset ehdot läpäisevät tarkistuksen. 3) Harkitse rajattua NIQ/Circana-POS-pilottia vasta myöhempänä varmennuskerroksena valituille maille.</x:v>
+        <x:v>1) The Germany evaluation extract has been received and privately audited. 2) Keep the wider 25/50/78-country subscription on HOLD until product, tax, channel and transaction-stage scope; source and record-status lineage; lender/buyer NDA data-room rights; and complete all-in commercial terms are confirmed in writing. 3) Treat the numerical pass as coherence evidence, not final accuracy or donor acceptance.
+FI: 1) Saksan arviointiote on vastaanotettu ja auditoitu yksityisesti. 2) Pidä laajempi 25/50/78 maan tilaus HOLD-tilassa, kunnes tuote-, vero-, kanava- ja tapahtumavaiheen rajaus, lähde- ja tietueiden tilalinja, lainanantaja-/ostaja-NDA-datahuoneoikeudet sekä täydelliset kaikki kustannukset kattavat kaupalliset ehdot on vahvistettu kirjallisesti. 3) Käsittele numeerista läpäisyä johdonmukaisuusnäyttönä, ei lopullisena tarkkuutena tai donor-hyväksyntänä.</x:v>
       </x:c>
       <x:c r="B10" s="60"/>
       <x:c r="C10" s="60"/>
@@ -2418,7 +2421,7 @@
     <x:mergeCell ref="A38:C39"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R413fb7489ddb49e8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R887ecea28d7f43b1"/>
 </x:worksheet>
 </file>
 
@@ -2621,13 +2624,13 @@
         <x:v>core_global_choose_one</x:v>
       </x:c>
       <x:c r="F7" s="132" t="str">
-        <x:v>Private indicative annual quotes received</x:v>
+        <x:v>Private indicative annual quotes received; Germany extract delivered</x:v>
       </x:c>
       <x:c r="G7" s="132" t="str">
-        <x:v>Continue evaluation, but do not activate the conditional Germany extract or buy before explicit purchase authority and a populated current 2022–2025 Germany test, reconciled 78/95 country-product-field-year coverage, category-specific method and record-status flags, a legally approved Pixan/NDA data-room Special Condition, and complete all-in commercial terms are confirmed. Buy at most one global master unless non-overlap is demonstrated.
-The expanded Germany sample permits a private 2023–2024 numerical liquid-volume comparison, but the product scope, retail-versus-tax stage and record-status bridge remain unresolved and the later 95-geography schema workbook has blank country-year value cells. A conditional paid Germany extract was offered on 2026-07-29; it has not been accepted or activated. End-consumer tax basis, restricted enterprise-AI processing and modelled Cyprus volume were clarified; NDA data-room rights, export and retention rights, taxes, fees and renewal terms remain open. No licensed values or private quote amounts are published.
-FI: Jatka arviointia, mutta älä aktivoi ehdollista Saksa-otetta tai osta ennen nimenomaista ostovaltuutusta ja ennen kuin täytetty ajantasainen Saksan 2022–2025-testi, täsmäytetty 78/95 maan maa–tuote–kenttä–vuosi-peitto, kategoriakohtainen menetelmä ja tietueiden tilamerkinnät, legal-tiimin hyväksymä Pixan-/NDA-datahuone-erityisehto sekä täydelliset kaikki kustannukset kattavat kaupalliset ehdot on vahvistettu. Osta enintään yksi globaali pääaineisto, ellei päällekkäisyyden puuttumista osoiteta.
-Laajennettu Saksa-näyte mahdollistaa yksityisen vuosien 2023–2024 numeerisen nestemäärävertailun, mutta tuoterajaus, vähittäis- ja verovaiheen ero sekä tietueiden tilasilta ovat ratkaisematta ja myöhemmän 95 maantieteen skeematyökirjan maa–vuosi-arvosolut ovat tyhjiä. Ehdollinen maksullinen Saksa-ote tarjottiin 29.7.2026; sitä ei ole hyväksytty tai aktivoitu. Loppuasiakasmyynnin veroperusta, rajattu yritystason tekoälykäsittely ja mallinnettu Kyproksen volyymi täsmennettiin; NDA-datahuoneoikeudet, vienti- ja säilytysoikeudet, verot, maksut ja uusimisehdot ovat avoinna. Lisensoituja arvoja tai yksityisiä tarjoushintoja ei julkaista.</x:v>
+        <x:v>Keep the wider 25/50/78-country subscription on HOLD. Proceed only after written clarification of the product, tax, channel and transaction-stage bridge; country-specific source and record-status lineage; exact field-year coverage; legally approved Pixan/lender/buyer/adviser NDA data-room rights; user, export, retention, cancellation and renewal terms; and complete all-in commercial terms. Buy at most one global master unless non-overlap is demonstrated.
+The full Germany extract passed the three preregistered numerical liquid-volume proximity tests in private review. This supports numerical coherence, not final accuracy or boundary equivalence. Licensed values and exact deviations remain private. G1 passes; G2, G3, G5 and G6 fail; G4 remains not testable. Germany remains outside the donor count and no wider subscription is authorised.
+FI: Pidä laajempi 25/50/78 maan tilaus HOLD-tilassa. Etene vasta, kun tuote-, vero-, kanava- ja tapahtumavaiheen silta, maakohtainen lähde- ja tietueiden tilalinja, täsmällinen kenttä–vuosi-peitto, legal-tiimin hyväksymät Pixan-/lainanantaja-/ostaja-/neuvonantaja-NDA-datahuoneoikeudet, käyttäjä-, vienti-, säilytys-, peruutus- ja uusimisehdot sekä täydelliset kaikki kustannukset kattavat kaupalliset ehdot on vahvistettu kirjallisesti. Osta enintään yksi globaali pääaineisto, ellei päällekkäisyyden puuttumista osoiteta.
+Saksan täysi ote läpäisi yksityisessä tarkastuksessa kolme ennalta rekisteröityä nestemäärän numeerista läheisyystestiä. Tämä tukee numeerista johdonmukaisuutta, ei lopullista tarkkuutta tai rajauksen vastaavuutta. Lisensoidut arvot ja tarkat poikkeamat pysyvät yksityisinä. G1 läpäisee; G2, G3, G5 ja G6 hylätään; G4 ei ole testattavissa. Saksa pysyy donor-määrän ulkopuolella eikä laajempaa tilausta ole valtuutettu.</x:v>
       </x:c>
       <x:c r="H7" s="133" t="n">
         <x:v>4</x:v>
@@ -4062,9 +4065,9 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="177" t="str">
-        <x:v>CURRENT RELEASE: 4 VENDORS TRACKED · 1 VENDOR ROUTE WITH SUBSTANTIVE RESPONSES · 0 SCORED · 0 PURCHASES AUTHORISED
+        <x:v>CURRENT RELEASE: 4 VENDORS TRACKED · 1 VENDOR ROUTE WITH SUBSTANTIVE RESPONSES · 1 GERMANY EVALUATION EXTRACT RECEIVED · 0 SCORED · 0 WIDER PACKAGES AUTHORISED
 Keep every score blank until all six mandatory gates read PASS. A missing input is NOT SCORED, never a zero.
-FI: NYKYJULKAISU: 4 TOIMITTAJAA SEURANNASSA · 1 TOIMITTAJAREITILLÄ SISÄLLÖLLISIÄ VASTAUKSIA · 0 PISTEYTETTY · 0 OSTOVALTUUTTA. Pidä pisteet tyhjinä, kunnes kaikki kuusi pakollista porttia ovat PASS-tilassa. Puuttuva tieto tarkoittaa EI PISTEYTETTY, ei nollaa.</x:v>
+FI: NYKYJULKAISU: 4 TOIMITTAJAA SEURANNASSA · 1 TOIMITTAJAREITILLÄ SISÄLLÖLLISIÄ VASTAUKSIA · 1 SAKSA-ARVIOINTIOTE VASTAANOTETTU · 0 PISTEYTETTY · 0 LAAJEMMAN PAKETIN OSTOVALTUUTTA. Pidä pisteet tyhjinä, kunnes kaikki kuusi pakollista porttia ovat PASS-tilassa. Puuttuva tieto tarkoittaa EI PISTEYTETTY, ei nollaa.</x:v>
       </x:c>
       <x:c r="B5" s="178"/>
       <x:c r="C5" s="178"/>
@@ -4366,11 +4369,11 @@
         <x:v>Passport Nicotine / e-vapour country series</x:v>
       </x:c>
       <x:c r="D15" s="81" t="str">
-        <x:v>CALL COMPLETED + CONDITIONAL PAID GERMANY EXTRACT OFFERED · NOT ACCEPTED · 0/6 GATES PASS · NOT SCORED
-FI: PUHELU PIDETTY + EHDOLLINEN MAKSULLINEN SAKSA-OTE TARJOTTU · EI HYVÄKSYTTY · 0/6 PORTTIA LÄPÄISTY · EI PISTEYTETTY</x:v>
+        <x:v>GERMANY EXTRACT DELIVERED + PRIVATE AUDIT COMPLETE · 1/6 GATES PASS · WIDER PACKAGE HOLD · NOT SCORED
+FI: SAKSA-OTE TOIMITETTU + YKSITYINEN AUDITOINTI VALMIS · 1/6 PORTTIA LÄPÄISTY · LAAJEMPI PAKETTI HOLD · EI PISTEYTETTY</x:v>
       </x:c>
       <x:c r="E15" s="192" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="F15" s="192" t="str">
         <x:v>OPEN</x:v>
@@ -4396,7 +4399,7 @@
       <x:c r="Q15" s="192"/>
       <x:c r="R15" s="194" t="str">
         <x:f>COUNTIF(E15:J15,"PASS")&amp;"/6"</x:f>
-        <x:v>0/6</x:v>
+        <x:v>1/6</x:v>
       </x:c>
       <x:c r="S15" s="194" t="str">
         <x:f>COUNT(K15:Q15)&amp;"/7"</x:f>
@@ -4415,7 +4418,7 @@
         <x:v>https://www.euromonitor.com/smokeless-tobacco-e-vapour-products-and-heated-tobacco-in-denmark/report</x:v>
       </x:c>
       <x:c r="X15" s="81" t="str">
-        <x:v>Status only. A conditional paid Germany extract was offered after the 2026-07-29 call. It has not been accepted or activated; no order, invoice, fee, subscription or commitment is authorised. Product scope, transaction-stage reconciliation, current Germany coverage, rights and all-in terms remain open. NOT SCORED; 0/6 gates pass.</x:v>
+        <x:v>Status only. The Germany extract was delivered and audited privately. The three preregistered numerical proximity tests passed, but licensed values remain withheld and scope, lineage, rights and all-in terms remain open. NOT SCORED; 1/6 gates pass; the wider package remains HOLD.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="84" customHeight="1">
